--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-13</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -556,10 +556,10 @@
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27021.686746988</v>
       </c>
       <c r="O4" t="n">
-        <v>54000</v>
+        <v>54043.373493976</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -2101,10 +2101,10 @@
         <v>63</v>
       </c>
       <c r="N42" t="n">
-        <v>15403.521040462</v>
+        <v>15403.521104651</v>
       </c>
       <c r="O42" t="n">
-        <v>970421.825549106</v>
+        <v>970421.8295930129</v>
       </c>
       <c r="P42" t="n">
         <v>33500</v>
@@ -7221,22 +7221,22 @@
         <v>0</v>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M159" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N159" t="n">
-        <v>10600</v>
+        <v>10603.665283541</v>
       </c>
       <c r="O159" t="n">
-        <v>1219000</v>
+        <v>1198214.177040133</v>
       </c>
       <c r="P159" t="n">
         <v>17200</v>
       </c>
       <c r="Q159" t="n">
-        <v>1978000</v>
+        <v>1943600</v>
       </c>
     </row>
     <row r="160">
@@ -7273,10 +7273,10 @@
         <v>69</v>
       </c>
       <c r="N160" t="n">
-        <v>5216.8959816133</v>
+        <v>5216.8959810174</v>
       </c>
       <c r="O160" t="n">
-        <v>359965.8227313177</v>
+        <v>359965.8226902006</v>
       </c>
       <c r="P160" t="n">
         <v>8500</v>
@@ -7589,22 +7589,22 @@
         <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M167" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N167" t="n">
         <v>5002</v>
       </c>
       <c r="O167" t="n">
-        <v>520208</v>
+        <v>510204</v>
       </c>
       <c r="P167" t="n">
         <v>8400</v>
       </c>
       <c r="Q167" t="n">
-        <v>873600</v>
+        <v>856800</v>
       </c>
     </row>
     <row r="168">
@@ -7681,22 +7681,22 @@
         <v>0</v>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M169" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N169" t="n">
         <v>6507</v>
       </c>
       <c r="O169" t="n">
-        <v>1529145</v>
+        <v>1516131</v>
       </c>
       <c r="P169" t="n">
         <v>9900</v>
       </c>
       <c r="Q169" t="n">
-        <v>2326500</v>
+        <v>2306700</v>
       </c>
     </row>
     <row r="170">
@@ -8582,22 +8582,22 @@
         <v>0</v>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N189" t="n">
-        <v>3594.2533147632</v>
+        <v>3596.7580209059</v>
       </c>
       <c r="O189" t="n">
-        <v>107827.599442896</v>
+        <v>104305.9826062711</v>
       </c>
       <c r="P189" t="n">
         <v>6500</v>
       </c>
       <c r="Q189" t="n">
-        <v>195000</v>
+        <v>188500</v>
       </c>
     </row>
     <row r="190">
@@ -9540,22 +9540,22 @@
         <v>0</v>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M210" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N210" t="n">
-        <v>4371.1712612367</v>
+        <v>4371.766707533</v>
       </c>
       <c r="O210" t="n">
-        <v>319095.5020702791</v>
+        <v>310395.436234843</v>
       </c>
       <c r="P210" t="n">
         <v>8900</v>
       </c>
       <c r="Q210" t="n">
-        <v>649700</v>
+        <v>631900</v>
       </c>
     </row>
     <row r="211">
@@ -9847,22 +9847,22 @@
         <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M217" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N217" t="n">
         <v>6242.93</v>
       </c>
       <c r="O217" t="n">
-        <v>299660.64</v>
+        <v>287174.78</v>
       </c>
       <c r="P217" t="n">
         <v>10400</v>
       </c>
       <c r="Q217" t="n">
-        <v>499200</v>
+        <v>478400</v>
       </c>
     </row>
     <row r="218">
@@ -10901,22 +10901,22 @@
         <v>0</v>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M240" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N240" t="n">
-        <v>2403.5165803524</v>
+        <v>2403.5166025127</v>
       </c>
       <c r="O240" t="n">
-        <v>420615.40156167</v>
+        <v>415808.3722346971</v>
       </c>
       <c r="P240" t="n">
         <v>3500</v>
       </c>
       <c r="Q240" t="n">
-        <v>612500</v>
+        <v>605500</v>
       </c>
     </row>
     <row r="241">
@@ -14030,22 +14030,22 @@
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M311" t="n">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="N311" t="n">
-        <v>1561.0035960591</v>
+        <v>1561.003634439</v>
       </c>
       <c r="O311" t="n">
-        <v>964700.2223645237</v>
+        <v>958456.231545546</v>
       </c>
       <c r="P311" t="n">
         <v>2900</v>
       </c>
       <c r="Q311" t="n">
-        <v>1792200</v>
+        <v>1780600</v>
       </c>
     </row>
     <row r="312">
@@ -23138,10 +23138,10 @@
         <v>356</v>
       </c>
       <c r="N509" t="n">
-        <v>1516.0387548048</v>
+        <v>1516.0387544268</v>
       </c>
       <c r="O509" t="n">
-        <v>539709.7967105088</v>
+        <v>539709.7965759408</v>
       </c>
       <c r="P509" t="n">
         <v>2300</v>
@@ -23322,10 +23322,10 @@
         <v>436</v>
       </c>
       <c r="N513" t="n">
-        <v>2079.3834819145</v>
+        <v>2079.3834145441</v>
       </c>
       <c r="O513" t="n">
-        <v>906611.198114722</v>
+        <v>906611.1687412276</v>
       </c>
       <c r="P513" t="n">
         <v>2900</v>
@@ -25218,22 +25218,22 @@
         <v>0</v>
       </c>
       <c r="L554" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M554" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N554" t="n">
-        <v>1690.8700092894</v>
+        <v>1690.870009298</v>
       </c>
       <c r="O554" t="n">
-        <v>292520.5116070662</v>
+        <v>289138.771589958</v>
       </c>
       <c r="P554" t="n">
         <v>3000</v>
       </c>
       <c r="Q554" t="n">
-        <v>519000</v>
+        <v>513000</v>
       </c>
     </row>
     <row r="555">
@@ -25454,10 +25454,10 @@
         <v>22</v>
       </c>
       <c r="N559" t="n">
-        <v>3907.5003375527</v>
+        <v>3907.5003418803</v>
       </c>
       <c r="O559" t="n">
-        <v>85965.0074261594</v>
+        <v>85965.0075213666</v>
       </c>
       <c r="P559" t="n">
         <v>3900</v>
@@ -26001,22 +26001,22 @@
         <v>0</v>
       </c>
       <c r="L571" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M571" t="n">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="N571" t="n">
-        <v>517.2940518305199</v>
+        <v>517.72052761748</v>
       </c>
       <c r="O571" t="n">
-        <v>123633.2783874943</v>
+        <v>118558.0008244029</v>
       </c>
       <c r="P571" t="n">
         <v>900</v>
       </c>
       <c r="Q571" t="n">
-        <v>215100</v>
+        <v>206100</v>
       </c>
     </row>
     <row r="572">
@@ -26186,22 +26186,22 @@
         <v>0</v>
       </c>
       <c r="L575" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M575" t="n">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="N575" t="n">
-        <v>703.79483731577</v>
+        <v>703.86725350482</v>
       </c>
       <c r="O575" t="n">
-        <v>646787.4554931927</v>
+        <v>641223.067942891</v>
       </c>
       <c r="P575" t="n">
         <v>900</v>
       </c>
       <c r="Q575" t="n">
-        <v>827100</v>
+        <v>819900</v>
       </c>
     </row>
     <row r="576">
@@ -30024,22 +30024,22 @@
         <v>0</v>
       </c>
       <c r="L655" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M655" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N655" t="n">
-        <v>8919.16</v>
+        <v>8975.6103797468</v>
       </c>
       <c r="O655" t="n">
-        <v>107029.92</v>
+        <v>98731.7141772148</v>
       </c>
       <c r="P655" t="n">
         <v>10000</v>
       </c>
       <c r="Q655" t="n">
-        <v>120000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="656">
@@ -31718,22 +31718,22 @@
         <v>0</v>
       </c>
       <c r="L691" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M691" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N691" t="n">
-        <v>5077</v>
+        <v>5150.0503597122</v>
       </c>
       <c r="O691" t="n">
-        <v>385852</v>
+        <v>381103.7266187028</v>
       </c>
       <c r="P691" t="n">
         <v>8500</v>
       </c>
       <c r="Q691" t="n">
-        <v>646000</v>
+        <v>629000</v>
       </c>
     </row>
     <row r="692">
@@ -34248,22 +34248,22 @@
         <v>0</v>
       </c>
       <c r="L746" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M746" t="n">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="N746" t="n">
         <v>9240</v>
       </c>
       <c r="O746" t="n">
-        <v>5257560</v>
+        <v>5220600</v>
       </c>
       <c r="P746" t="n">
         <v>11500</v>
       </c>
       <c r="Q746" t="n">
-        <v>6543500</v>
+        <v>6497500</v>
       </c>
     </row>
     <row r="747">
@@ -34294,22 +34294,22 @@
         <v>0</v>
       </c>
       <c r="L747" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M747" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N747" t="n">
         <v>2288</v>
       </c>
       <c r="O747" t="n">
-        <v>86944</v>
+        <v>84656</v>
       </c>
       <c r="P747" t="n">
         <v>2900</v>
       </c>
       <c r="Q747" t="n">
-        <v>110200</v>
+        <v>107300</v>
       </c>
     </row>
     <row r="748">
@@ -34340,22 +34340,22 @@
         <v>0</v>
       </c>
       <c r="L748" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M748" t="n">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="N748" t="n">
-        <v>7216</v>
+        <v>7360.32</v>
       </c>
       <c r="O748" t="n">
-        <v>909216</v>
+        <v>736032</v>
       </c>
       <c r="P748" t="n">
         <v>9000</v>
       </c>
       <c r="Q748" t="n">
-        <v>1134000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="749">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -3864,10 +3864,10 @@
         <v>3</v>
       </c>
       <c r="N82" t="n">
-        <v>141416.88462046</v>
+        <v>141885.15245033</v>
       </c>
       <c r="O82" t="n">
-        <v>424250.6538613801</v>
+        <v>425655.45735099</v>
       </c>
       <c r="P82" t="n">
         <v>251900</v>
@@ -3906,10 +3906,10 @@
         <v>4</v>
       </c>
       <c r="N83" t="n">
-        <v>200072.20216981</v>
+        <v>201977.65171429</v>
       </c>
       <c r="O83" t="n">
-        <v>800288.8086792401</v>
+        <v>807910.60685716</v>
       </c>
       <c r="P83" t="n">
         <v>312000</v>
@@ -4234,10 +4234,10 @@
         <v>9</v>
       </c>
       <c r="N91" t="n">
-        <v>61666.874171271</v>
+        <v>62706.203511236</v>
       </c>
       <c r="O91" t="n">
-        <v>555001.867541439</v>
+        <v>564355.831601124</v>
       </c>
       <c r="P91" t="n">
         <v>98900</v>
@@ -7181,10 +7181,10 @@
         <v>182</v>
       </c>
       <c r="N158" t="n">
-        <v>2582.2551367187</v>
+        <v>2582.2551307749</v>
       </c>
       <c r="O158" t="n">
-        <v>469970.4348828034</v>
+        <v>469970.4338010318</v>
       </c>
       <c r="P158" t="n">
         <v>4500</v>
@@ -10727,10 +10727,10 @@
         <v>63</v>
       </c>
       <c r="N236" t="n">
-        <v>11921.4</v>
+        <v>11949.761776368</v>
       </c>
       <c r="O236" t="n">
-        <v>751048.2</v>
+        <v>752834.9919111839</v>
       </c>
       <c r="P236" t="n">
         <v>19900</v>
@@ -10907,10 +10907,10 @@
         <v>170</v>
       </c>
       <c r="N240" t="n">
-        <v>2403.516914488</v>
+        <v>2403.5169237057</v>
       </c>
       <c r="O240" t="n">
-        <v>408597.87546296</v>
+        <v>408597.8770299689</v>
       </c>
       <c r="P240" t="n">
         <v>3500</v>
@@ -13054,10 +13054,10 @@
         <v>54</v>
       </c>
       <c r="N289" t="n">
-        <v>4814.2679274047</v>
+        <v>4814.2679269747</v>
       </c>
       <c r="O289" t="n">
-        <v>259970.4680798538</v>
+        <v>259970.4680566338</v>
       </c>
       <c r="P289" t="n">
         <v>9900</v>
@@ -13816,10 +13816,10 @@
         <v>28</v>
       </c>
       <c r="N306" t="n">
-        <v>16974.69</v>
+        <v>17078.829202454</v>
       </c>
       <c r="O306" t="n">
-        <v>475291.3199999999</v>
+        <v>478207.217668712</v>
       </c>
       <c r="P306" t="n">
         <v>26900</v>
@@ -14474,10 +14474,10 @@
         <v>57</v>
       </c>
       <c r="N321" t="n">
-        <v>9627.34</v>
+        <v>11147.446315789</v>
       </c>
       <c r="O321" t="n">
-        <v>548758.38</v>
+        <v>635404.4399999731</v>
       </c>
       <c r="P321" t="n">
         <v>15900</v>
@@ -14982,10 +14982,10 @@
         <v>231</v>
       </c>
       <c r="N332" t="n">
-        <v>7700</v>
+        <v>7812.5456760049</v>
       </c>
       <c r="O332" t="n">
-        <v>1778700</v>
+        <v>1804698.051157132</v>
       </c>
       <c r="P332" t="n">
         <v>13900</v>
@@ -15442,10 +15442,10 @@
         <v>88</v>
       </c>
       <c r="N342" t="n">
-        <v>5218.1705812417</v>
+        <v>5218.1705827815</v>
       </c>
       <c r="O342" t="n">
-        <v>459199.0111492696</v>
+        <v>459199.011284772</v>
       </c>
       <c r="P342" t="n">
         <v>8500</v>
@@ -23138,10 +23138,10 @@
         <v>340</v>
       </c>
       <c r="N509" t="n">
-        <v>1516.0387516479</v>
+        <v>1516.0387513947</v>
       </c>
       <c r="O509" t="n">
-        <v>515453.175560286</v>
+        <v>515453.175474198</v>
       </c>
       <c r="P509" t="n">
         <v>2300</v>
@@ -26007,10 +26007,10 @@
         <v>203</v>
       </c>
       <c r="N571" t="n">
-        <v>517.29416017244</v>
+        <v>517.81142476254</v>
       </c>
       <c r="O571" t="n">
-        <v>105010.7145150053</v>
+        <v>105115.7192267956</v>
       </c>
       <c r="P571" t="n">
         <v>900</v>
@@ -26192,10 +26192,10 @@
         <v>865</v>
       </c>
       <c r="N575" t="n">
-        <v>703.79482873668</v>
+        <v>703.79482793718</v>
       </c>
       <c r="O575" t="n">
-        <v>608782.5268572281</v>
+        <v>608782.5261656607</v>
       </c>
       <c r="P575" t="n">
         <v>900</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -950,10 +950,10 @@
         <v>99</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3087912088</v>
+        <v>1811.3088176353</v>
       </c>
       <c r="O13" t="n">
-        <v>179319.5703296712</v>
+        <v>179319.5729458947</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -3053,10 +3053,10 @@
         <v>14</v>
       </c>
       <c r="N63" t="n">
-        <v>16486.407586207</v>
+        <v>16486.407256637</v>
       </c>
       <c r="O63" t="n">
-        <v>230809.706206898</v>
+        <v>230809.701592918</v>
       </c>
       <c r="P63" t="n">
         <v>30500</v>
@@ -7319,10 +7319,10 @@
         <v>663</v>
       </c>
       <c r="N161" t="n">
-        <v>3158.8608362663</v>
+        <v>3158.8608369301</v>
       </c>
       <c r="O161" t="n">
-        <v>2094324.734444557</v>
+        <v>2094324.734884656</v>
       </c>
       <c r="P161" t="n">
         <v>5600</v>
@@ -7733,10 +7733,10 @@
         <v>168</v>
       </c>
       <c r="N170" t="n">
-        <v>3795.7100076147</v>
+        <v>3795.7100076161</v>
       </c>
       <c r="O170" t="n">
-        <v>637679.2812792696</v>
+        <v>637679.2812795048</v>
       </c>
       <c r="P170" t="n">
         <v>6200</v>
@@ -8273,10 +8273,10 @@
         <v>82</v>
       </c>
       <c r="N182" t="n">
-        <v>2267.0481062554</v>
+        <v>2267.0481021898</v>
       </c>
       <c r="O182" t="n">
-        <v>185897.9447129428</v>
+        <v>185897.9443795636</v>
       </c>
       <c r="P182" t="n">
         <v>3900</v>
@@ -9638,10 +9638,10 @@
         <v>159</v>
       </c>
       <c r="N212" t="n">
-        <v>1592.5654585153</v>
+        <v>1592.5654545455</v>
       </c>
       <c r="O212" t="n">
-        <v>253217.9079039327</v>
+        <v>253217.9072727345</v>
       </c>
       <c r="P212" t="n">
         <v>3900</v>
@@ -10953,10 +10953,10 @@
         <v>167</v>
       </c>
       <c r="N241" t="n">
-        <v>2403.5172431982</v>
+        <v>2403.5172815804</v>
       </c>
       <c r="O241" t="n">
-        <v>401387.3796140994</v>
+        <v>401387.3860239268</v>
       </c>
       <c r="P241" t="n">
         <v>3500</v>
@@ -12093,10 +12093,10 @@
         <v>159</v>
       </c>
       <c r="N267" t="n">
-        <v>2029.8740849673</v>
+        <v>2029.874091653</v>
       </c>
       <c r="O267" t="n">
-        <v>322749.9795098007</v>
+        <v>322749.980572827</v>
       </c>
       <c r="P267" t="n">
         <v>3600</v>
@@ -19375,10 +19375,10 @@
         <v>147</v>
       </c>
       <c r="N427" t="n">
-        <v>4907.8225450902</v>
+        <v>4907.8225656566</v>
       </c>
       <c r="O427" t="n">
-        <v>721449.9141282594</v>
+        <v>721449.9171515203</v>
       </c>
       <c r="P427" t="n">
         <v>8200</v>
@@ -23184,10 +23184,10 @@
         <v>340</v>
       </c>
       <c r="N510" t="n">
-        <v>1516.0387513947</v>
+        <v>1516.0387508879</v>
       </c>
       <c r="O510" t="n">
-        <v>515453.175474198</v>
+        <v>515453.175301886</v>
       </c>
       <c r="P510" t="n">
         <v>2300</v>
@@ -23414,10 +23414,10 @@
         <v>135</v>
       </c>
       <c r="N515" t="n">
-        <v>1803.0164892802</v>
+        <v>1803.016504221</v>
       </c>
       <c r="O515" t="n">
-        <v>243407.226052827</v>
+        <v>243407.228069835</v>
       </c>
       <c r="P515" t="n">
         <v>2500</v>
@@ -23598,10 +23598,10 @@
         <v>264</v>
       </c>
       <c r="N519" t="n">
-        <v>2056.0823128492</v>
+        <v>2056.0822725571</v>
       </c>
       <c r="O519" t="n">
-        <v>542805.7305921889</v>
+        <v>542805.7199550745</v>
       </c>
       <c r="P519" t="n">
         <v>2900</v>
@@ -23918,10 +23918,10 @@
         <v>9</v>
       </c>
       <c r="N526" t="n">
-        <v>2546.982132964</v>
+        <v>2546.9817919075</v>
       </c>
       <c r="O526" t="n">
-        <v>22922.839196676</v>
+        <v>22922.8361271675</v>
       </c>
       <c r="P526" t="n">
         <v>3900</v>
@@ -26053,10 +26053,10 @@
         <v>167</v>
       </c>
       <c r="N572" t="n">
-        <v>517.29429288703</v>
+        <v>517.29430006698</v>
       </c>
       <c r="O572" t="n">
-        <v>86388.14691213401</v>
+        <v>86388.14811118566</v>
       </c>
       <c r="P572" t="n">
         <v>900</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -1223,10 +1223,10 @@
         <v>55</v>
       </c>
       <c r="N20" t="n">
-        <v>4088.8962655602</v>
+        <v>4072</v>
       </c>
       <c r="O20" t="n">
-        <v>224889.294605811</v>
+        <v>223960</v>
       </c>
       <c r="P20" t="n">
         <v>7500</v>
@@ -3095,10 +3095,10 @@
         <v>39</v>
       </c>
       <c r="N64" t="n">
-        <v>15899.011607143</v>
+        <v>15711.964345238</v>
       </c>
       <c r="O64" t="n">
-        <v>620061.452678577</v>
+        <v>612766.6094642821</v>
       </c>
       <c r="P64" t="n">
         <v>28500</v>
@@ -4862,10 +4862,10 @@
         <v>26</v>
       </c>
       <c r="N105" t="n">
-        <v>544.6367953668</v>
+        <v>538.40061776062</v>
       </c>
       <c r="O105" t="n">
-        <v>14160.5566795368</v>
+        <v>13998.41606177612</v>
       </c>
       <c r="P105" t="n">
         <v>6800</v>
@@ -5287,10 +5287,10 @@
         <v>3</v>
       </c>
       <c r="N115" t="n">
-        <v>2644.1214388489</v>
+        <v>2570.16</v>
       </c>
       <c r="O115" t="n">
-        <v>7932.3643165467</v>
+        <v>7710.48</v>
       </c>
       <c r="P115" t="n">
         <v>4700</v>
@@ -5713,10 +5713,10 @@
         <v>85</v>
       </c>
       <c r="N125" t="n">
-        <v>2659.1657943925</v>
+        <v>2563.34</v>
       </c>
       <c r="O125" t="n">
-        <v>226029.0925233625</v>
+        <v>217883.9</v>
       </c>
       <c r="P125" t="n">
         <v>4700</v>
@@ -6210,10 +6210,10 @@
         <v>41</v>
       </c>
       <c r="N136" t="n">
-        <v>10897.588251121</v>
+        <v>10752.93</v>
       </c>
       <c r="O136" t="n">
-        <v>446801.118295961</v>
+        <v>440870.13</v>
       </c>
       <c r="P136" t="n">
         <v>18400</v>
@@ -6256,10 +6256,10 @@
         <v>2</v>
       </c>
       <c r="N137" t="n">
-        <v>27515</v>
+        <v>16509</v>
       </c>
       <c r="O137" t="n">
-        <v>55030</v>
+        <v>33018</v>
       </c>
       <c r="P137" t="n">
         <v>11500</v>
@@ -6825,10 +6825,10 @@
         <v>20</v>
       </c>
       <c r="N150" t="n">
-        <v>12796.783333333</v>
+        <v>12587</v>
       </c>
       <c r="O150" t="n">
-        <v>255935.66666666</v>
+        <v>251740</v>
       </c>
       <c r="P150" t="n">
         <v>18900</v>
@@ -8273,10 +8273,10 @@
         <v>82</v>
       </c>
       <c r="N182" t="n">
-        <v>2271.9151051954</v>
+        <v>2267.0481021898</v>
       </c>
       <c r="O182" t="n">
-        <v>186297.0386260228</v>
+        <v>185897.9443795636</v>
       </c>
       <c r="P182" t="n">
         <v>3900</v>
@@ -8634,10 +8634,10 @@
         <v>41</v>
       </c>
       <c r="N190" t="n">
-        <v>3594.2531182796</v>
+        <v>3594.2531034483</v>
       </c>
       <c r="O190" t="n">
-        <v>147364.3778494636</v>
+        <v>147364.3772413803</v>
       </c>
       <c r="P190" t="n">
         <v>6500</v>
@@ -9324,10 +9324,10 @@
         <v>3</v>
       </c>
       <c r="N205" t="n">
-        <v>2718.841814346</v>
+        <v>2696.09</v>
       </c>
       <c r="O205" t="n">
-        <v>8156.525443037999</v>
+        <v>8088.27</v>
       </c>
       <c r="P205" t="n">
         <v>8200</v>
@@ -9899,10 +9899,10 @@
         <v>124</v>
       </c>
       <c r="N218" t="n">
-        <v>6260.7161253561</v>
+        <v>6242.93</v>
       </c>
       <c r="O218" t="n">
-        <v>776328.7995441564</v>
+        <v>774123.3200000001</v>
       </c>
       <c r="P218" t="n">
         <v>10400</v>
@@ -10407,10 +10407,10 @@
         <v>188</v>
       </c>
       <c r="N229" t="n">
-        <v>4752.0246648045</v>
+        <v>4635.49</v>
       </c>
       <c r="O229" t="n">
-        <v>893380.6369832461</v>
+        <v>871472.12</v>
       </c>
       <c r="P229" t="n">
         <v>7500</v>
@@ -10999,10 +10999,10 @@
         <v>10</v>
       </c>
       <c r="N242" t="n">
-        <v>17733.6</v>
+        <v>14778</v>
       </c>
       <c r="O242" t="n">
-        <v>177336</v>
+        <v>147780</v>
       </c>
       <c r="P242" t="n">
         <v>24900</v>
@@ -11040,10 +11040,10 @@
         <v>39</v>
       </c>
       <c r="N243" t="n">
-        <v>11749.140699301</v>
+        <v>11507.72</v>
       </c>
       <c r="O243" t="n">
-        <v>458216.487272739</v>
+        <v>448801.08</v>
       </c>
       <c r="P243" t="n">
         <v>25800</v>
@@ -13054,10 +13054,10 @@
         <v>60</v>
       </c>
       <c r="N289" t="n">
-        <v>30262.214828189</v>
+        <v>30244.600034945</v>
       </c>
       <c r="O289" t="n">
-        <v>1815732.88969134</v>
+        <v>1814676.0020967</v>
       </c>
       <c r="P289" t="n">
         <v>48900</v>
@@ -13550,10 +13550,10 @@
         <v>2</v>
       </c>
       <c r="N300" t="n">
-        <v>27637.186666667</v>
+        <v>20727.89</v>
       </c>
       <c r="O300" t="n">
-        <v>55274.373333334</v>
+        <v>41455.78</v>
       </c>
       <c r="P300" t="n">
         <v>33500</v>
@@ -13596,10 +13596,10 @@
         <v>10</v>
       </c>
       <c r="N301" t="n">
-        <v>15768.141666667</v>
+        <v>13515.55</v>
       </c>
       <c r="O301" t="n">
-        <v>157681.41666667</v>
+        <v>135155.5</v>
       </c>
       <c r="P301" t="n">
         <v>30900</v>
@@ -13688,10 +13688,10 @@
         <v>7</v>
       </c>
       <c r="N303" t="n">
-        <v>27233.355818182</v>
+        <v>27123.764828283</v>
       </c>
       <c r="O303" t="n">
-        <v>190633.490727274</v>
+        <v>189866.353797981</v>
       </c>
       <c r="P303" t="n">
         <v>44500</v>
@@ -14036,10 +14036,10 @@
         <v>583</v>
       </c>
       <c r="N311" t="n">
-        <v>1561.0041954445</v>
+        <v>1561.004375</v>
       </c>
       <c r="O311" t="n">
-        <v>910065.4459441436</v>
+        <v>910065.550625</v>
       </c>
       <c r="P311" t="n">
         <v>2900</v>
@@ -14346,10 +14346,10 @@
         <v>138</v>
       </c>
       <c r="N318" t="n">
-        <v>7988.3991280864</v>
+        <v>7969.9501697531</v>
       </c>
       <c r="O318" t="n">
-        <v>1102399.079675923</v>
+        <v>1099853.123425928</v>
       </c>
       <c r="P318" t="n">
         <v>12900</v>
@@ -14474,10 +14474,10 @@
         <v>54</v>
       </c>
       <c r="N321" t="n">
-        <v>9794.2880924855</v>
+        <v>9627.34</v>
       </c>
       <c r="O321" t="n">
-        <v>528891.556994217</v>
+        <v>519876.36</v>
       </c>
       <c r="P321" t="n">
         <v>15900</v>
@@ -15074,10 +15074,10 @@
         <v>120</v>
       </c>
       <c r="N334" t="n">
-        <v>2647.8160651629</v>
+        <v>2634.61</v>
       </c>
       <c r="O334" t="n">
-        <v>317737.927819548</v>
+        <v>316153.2</v>
       </c>
       <c r="P334" t="n">
         <v>4200</v>
@@ -15120,10 +15120,10 @@
         <v>53</v>
       </c>
       <c r="N335" t="n">
-        <v>3131.5075106082</v>
+        <v>3113.8900282885</v>
       </c>
       <c r="O335" t="n">
-        <v>165969.8980622346</v>
+        <v>165036.1714992905</v>
       </c>
       <c r="P335" t="n">
         <v>5000</v>
@@ -15304,10 +15304,10 @@
         <v>1</v>
       </c>
       <c r="N339" t="n">
-        <v>4397.0456179775</v>
+        <v>4163.1602247191</v>
       </c>
       <c r="O339" t="n">
-        <v>4397.0456179775</v>
+        <v>4163.1602247191</v>
       </c>
       <c r="P339" t="n">
         <v>6700</v>
@@ -15350,10 +15350,10 @@
         <v>209</v>
       </c>
       <c r="N340" t="n">
-        <v>2510.8902747909</v>
+        <v>2495.98</v>
       </c>
       <c r="O340" t="n">
-        <v>524776.0674312981</v>
+        <v>521659.82</v>
       </c>
       <c r="P340" t="n">
         <v>4100</v>
@@ -15672,10 +15672,10 @@
         <v>1</v>
       </c>
       <c r="N347" t="n">
-        <v>5859.18</v>
+        <v>5791.05</v>
       </c>
       <c r="O347" t="n">
-        <v>5859.18</v>
+        <v>5791.05</v>
       </c>
       <c r="P347" t="n">
         <v>9300</v>
@@ -15721,10 +15721,10 @@
         <v>20</v>
       </c>
       <c r="N348" t="n">
-        <v>9379.0968275862</v>
+        <v>9188.98</v>
       </c>
       <c r="O348" t="n">
-        <v>187581.936551724</v>
+        <v>183779.6</v>
       </c>
       <c r="P348" t="n">
         <v>12900</v>
@@ -16365,10 +16365,10 @@
         <v>59</v>
       </c>
       <c r="N362" t="n">
-        <v>16092.984749455</v>
+        <v>16058</v>
       </c>
       <c r="O362" t="n">
-        <v>949486.1002178449</v>
+        <v>947422</v>
       </c>
       <c r="P362" t="n">
         <v>25900</v>
@@ -16411,10 +16411,10 @@
         <v>25</v>
       </c>
       <c r="N363" t="n">
-        <v>25576.890257559</v>
+        <v>25534</v>
       </c>
       <c r="O363" t="n">
-        <v>639422.256438975</v>
+        <v>638350</v>
       </c>
       <c r="P363" t="n">
         <v>40900</v>
@@ -16736,10 +16736,10 @@
         <v>7</v>
       </c>
       <c r="N370" t="n">
-        <v>9927.272727272701</v>
+        <v>9750</v>
       </c>
       <c r="O370" t="n">
-        <v>69490.9090909089</v>
+        <v>68250</v>
       </c>
       <c r="P370" t="n">
         <v>15600</v>
@@ -16828,10 +16828,10 @@
         <v>70</v>
       </c>
       <c r="N372" t="n">
-        <v>7278.6868686869</v>
+        <v>7230</v>
       </c>
       <c r="O372" t="n">
-        <v>509508.080808083</v>
+        <v>506100</v>
       </c>
       <c r="P372" t="n">
         <v>11600</v>
@@ -17897,10 +17897,10 @@
         <v>31</v>
       </c>
       <c r="N395" t="n">
-        <v>13795.055263158</v>
+        <v>13687</v>
       </c>
       <c r="O395" t="n">
-        <v>427646.713157898</v>
+        <v>424297</v>
       </c>
       <c r="P395" t="n">
         <v>21900</v>
@@ -18127,10 +18127,10 @@
         <v>19</v>
       </c>
       <c r="N400" t="n">
-        <v>20960.318181818</v>
+        <v>20049</v>
       </c>
       <c r="O400" t="n">
-        <v>398246.045454542</v>
+        <v>380931</v>
       </c>
       <c r="P400" t="n">
         <v>32900</v>
@@ -18360,10 +18360,10 @@
         <v>22</v>
       </c>
       <c r="N405" t="n">
-        <v>10485.899280576</v>
+        <v>10411</v>
       </c>
       <c r="O405" t="n">
-        <v>230689.784172672</v>
+        <v>229042</v>
       </c>
       <c r="P405" t="n">
         <v>16900</v>
@@ -18869,10 +18869,10 @@
         <v>41</v>
       </c>
       <c r="N416" t="n">
-        <v>32566.857142857</v>
+        <v>32332</v>
       </c>
       <c r="O416" t="n">
-        <v>1335241.142857137</v>
+        <v>1325612</v>
       </c>
       <c r="P416" t="n">
         <v>55900</v>
@@ -19191,10 +19191,10 @@
         <v>65</v>
       </c>
       <c r="N423" t="n">
-        <v>3412.5148218527</v>
+        <v>3396.38</v>
       </c>
       <c r="O423" t="n">
-        <v>221813.4634204255</v>
+        <v>220764.7</v>
       </c>
       <c r="P423" t="n">
         <v>6500</v>
@@ -19421,10 +19421,10 @@
         <v>23</v>
       </c>
       <c r="N428" t="n">
-        <v>23932.94</v>
+        <v>23376.36</v>
       </c>
       <c r="O428" t="n">
-        <v>550457.62</v>
+        <v>537656.28</v>
       </c>
       <c r="P428" t="n">
         <v>40900</v>
@@ -19467,10 +19467,10 @@
         <v>16</v>
       </c>
       <c r="N429" t="n">
-        <v>13233.257042254</v>
+        <v>13210</v>
       </c>
       <c r="O429" t="n">
-        <v>211732.112676064</v>
+        <v>211360</v>
       </c>
       <c r="P429" t="n">
         <v>23900</v>
@@ -19733,10 +19733,10 @@
         <v>1</v>
       </c>
       <c r="N435" t="n">
-        <v>36516.685818182</v>
+        <v>35864.602181818</v>
       </c>
       <c r="O435" t="n">
-        <v>36516.685818182</v>
+        <v>35864.602181818</v>
       </c>
       <c r="P435" t="n">
         <v>62900</v>
@@ -20101,10 +20101,10 @@
         <v>34</v>
       </c>
       <c r="N443" t="n">
-        <v>12498.870967742</v>
+        <v>11922</v>
       </c>
       <c r="O443" t="n">
-        <v>424961.612903228</v>
+        <v>405348</v>
       </c>
       <c r="P443" t="n">
         <v>19900</v>
@@ -20239,10 +20239,10 @@
         <v>144</v>
       </c>
       <c r="N446" t="n">
-        <v>2657.2435094002</v>
+        <v>2629</v>
       </c>
       <c r="O446" t="n">
-        <v>382643.0653536288</v>
+        <v>378576</v>
       </c>
       <c r="P446" t="n">
         <v>4500</v>
@@ -20331,10 +20331,10 @@
         <v>14</v>
       </c>
       <c r="N448" t="n">
-        <v>6881.8463298379</v>
+        <v>6849.2</v>
       </c>
       <c r="O448" t="n">
-        <v>96345.8486177306</v>
+        <v>95888.8</v>
       </c>
       <c r="P448" t="n">
         <v>11500</v>
@@ -20791,10 +20791,10 @@
         <v>67</v>
       </c>
       <c r="N458" t="n">
-        <v>7639.2713286713</v>
+        <v>7635</v>
       </c>
       <c r="O458" t="n">
-        <v>511831.1790209771</v>
+        <v>511545</v>
       </c>
       <c r="P458" t="n">
         <v>13900</v>
@@ -21251,10 +21251,10 @@
         <v>19</v>
       </c>
       <c r="N468" t="n">
-        <v>11478.737327189</v>
+        <v>11348</v>
       </c>
       <c r="O468" t="n">
-        <v>218096.009216591</v>
+        <v>215612</v>
       </c>
       <c r="P468" t="n">
         <v>19900</v>
@@ -22215,10 +22215,10 @@
         <v>8</v>
       </c>
       <c r="N489" t="n">
-        <v>14369.318181818</v>
+        <v>14050</v>
       </c>
       <c r="O489" t="n">
-        <v>114954.545454544</v>
+        <v>112400</v>
       </c>
       <c r="P489" t="n">
         <v>23900</v>
@@ -22261,10 +22261,10 @@
         <v>35</v>
       </c>
       <c r="N490" t="n">
-        <v>8721.3759213759</v>
+        <v>8700</v>
       </c>
       <c r="O490" t="n">
-        <v>305248.1572481565</v>
+        <v>304500</v>
       </c>
       <c r="P490" t="n">
         <v>14900</v>
@@ -22583,10 +22583,10 @@
         <v>9</v>
       </c>
       <c r="N497" t="n">
-        <v>21884.258426966</v>
+        <v>21762</v>
       </c>
       <c r="O497" t="n">
-        <v>196958.325842694</v>
+        <v>195858</v>
       </c>
       <c r="P497" t="n">
         <v>35900</v>
@@ -22629,10 +22629,10 @@
         <v>223</v>
       </c>
       <c r="N498" t="n">
-        <v>3823.6153319644</v>
+        <v>3821</v>
       </c>
       <c r="O498" t="n">
-        <v>852666.2190280611</v>
+        <v>852083</v>
       </c>
       <c r="P498" t="n">
         <v>5900</v>
@@ -22767,10 +22767,10 @@
         <v>23</v>
       </c>
       <c r="N501" t="n">
-        <v>50038.3125</v>
+        <v>48522</v>
       </c>
       <c r="O501" t="n">
-        <v>1150881.1875</v>
+        <v>1116006</v>
       </c>
       <c r="P501" t="n">
         <v>77900</v>
@@ -22859,10 +22859,10 @@
         <v>149</v>
       </c>
       <c r="N503" t="n">
-        <v>7295.3326848249</v>
+        <v>7253</v>
       </c>
       <c r="O503" t="n">
-        <v>1087004.57003891</v>
+        <v>1080697</v>
       </c>
       <c r="P503" t="n">
         <v>11900</v>
@@ -23826,10 +23826,10 @@
         <v>7</v>
       </c>
       <c r="N524" t="n">
-        <v>2546.9807189542</v>
+        <v>2546.9805333333</v>
       </c>
       <c r="O524" t="n">
-        <v>17828.8650326794</v>
+        <v>17828.8637333331</v>
       </c>
       <c r="P524" t="n">
         <v>3900</v>
@@ -24097,10 +24097,10 @@
         <v>2458</v>
       </c>
       <c r="N530" t="n">
-        <v>1955.7828121686</v>
+        <v>1955.2371130338</v>
       </c>
       <c r="O530" t="n">
-        <v>4807314.152310419</v>
+        <v>4805972.82383708</v>
       </c>
       <c r="P530" t="n">
         <v>3000</v>
@@ -24143,10 +24143,10 @@
         <v>3423</v>
       </c>
       <c r="N531" t="n">
-        <v>1185.8146867168</v>
+        <v>1185.3195655806</v>
       </c>
       <c r="O531" t="n">
-        <v>4059043.672631606</v>
+        <v>4057348.872982394</v>
       </c>
       <c r="P531" t="n">
         <v>1900</v>
@@ -24527,10 +24527,10 @@
         <v>39</v>
       </c>
       <c r="N539" t="n">
-        <v>3256.3775316456</v>
+        <v>3026.5160126582</v>
       </c>
       <c r="O539" t="n">
-        <v>126998.7237341784</v>
+        <v>118034.1244936698</v>
       </c>
       <c r="P539" t="n">
         <v>7000</v>
@@ -24674,10 +24674,10 @@
         <v>227</v>
       </c>
       <c r="N542" t="n">
-        <v>1537.958258381</v>
+        <v>1530.4499182339</v>
       </c>
       <c r="O542" t="n">
-        <v>349116.524652487</v>
+        <v>347412.1314390953</v>
       </c>
       <c r="P542" t="n">
         <v>2600</v>
@@ -25367,10 +25367,10 @@
         <v>37</v>
       </c>
       <c r="N557" t="n">
-        <v>8915.3355918367</v>
+        <v>8702.219999999999</v>
       </c>
       <c r="O557" t="n">
-        <v>329867.4168979579</v>
+        <v>321982.14</v>
       </c>
       <c r="P557" t="n">
         <v>8900</v>
@@ -25509,10 +25509,10 @@
         <v>10</v>
       </c>
       <c r="N560" t="n">
-        <v>25221.936</v>
+        <v>21018.28</v>
       </c>
       <c r="O560" t="n">
-        <v>252219.36</v>
+        <v>210182.8</v>
       </c>
       <c r="P560" t="n">
         <v>23500</v>
@@ -26198,10 +26198,10 @@
         <v>425</v>
       </c>
       <c r="N575" t="n">
-        <v>703.7947715550901</v>
+        <v>704.67584580877</v>
       </c>
       <c r="O575" t="n">
-        <v>299112.7779109133</v>
+        <v>299487.2344687273</v>
       </c>
       <c r="P575" t="n">
         <v>900</v>
@@ -26636,10 +26636,10 @@
         <v>5</v>
       </c>
       <c r="N584" t="n">
-        <v>29180.918333333</v>
+        <v>21885.688333333</v>
       </c>
       <c r="O584" t="n">
-        <v>145904.591666665</v>
+        <v>109428.441666665</v>
       </c>
       <c r="P584" t="n">
         <v>33500</v>
@@ -27586,10 +27586,10 @@
         <v>10</v>
       </c>
       <c r="N604" t="n">
-        <v>26089.656666667</v>
+        <v>24082.76</v>
       </c>
       <c r="O604" t="n">
-        <v>260896.56666667</v>
+        <v>240827.6</v>
       </c>
       <c r="P604" t="n">
         <v>56900</v>
@@ -28413,10 +28413,10 @@
         <v>11</v>
       </c>
       <c r="N621" t="n">
-        <v>14616.494117647</v>
+        <v>12424.02</v>
       </c>
       <c r="O621" t="n">
-        <v>160781.435294117</v>
+        <v>136664.22</v>
       </c>
       <c r="P621" t="n">
         <v>17500</v>
@@ -29087,10 +29087,10 @@
         <v>109</v>
       </c>
       <c r="N635" t="n">
-        <v>5370.6369361702</v>
+        <v>5347.88</v>
       </c>
       <c r="O635" t="n">
-        <v>585399.4260425518</v>
+        <v>582918.92</v>
       </c>
       <c r="P635" t="n">
         <v>7900</v>
@@ -29136,10 +29136,10 @@
         <v>114</v>
       </c>
       <c r="N636" t="n">
-        <v>4593.1990728477</v>
+        <v>4578.04</v>
       </c>
       <c r="O636" t="n">
-        <v>523624.6943046378</v>
+        <v>521896.56</v>
       </c>
       <c r="P636" t="n">
         <v>7500</v>
@@ -29987,10 +29987,10 @@
         <v>6</v>
       </c>
       <c r="N654" t="n">
-        <v>10912.902659574</v>
+        <v>10798.03</v>
       </c>
       <c r="O654" t="n">
-        <v>65477.415957444</v>
+        <v>64788.18000000001</v>
       </c>
       <c r="P654" t="n">
         <v>45000</v>
@@ -30128,10 +30128,10 @@
         <v>19</v>
       </c>
       <c r="N657" t="n">
-        <v>5272.2028268551</v>
+        <v>5216.9</v>
       </c>
       <c r="O657" t="n">
-        <v>100171.8537102469</v>
+        <v>99121.09999999999</v>
       </c>
       <c r="P657" t="n">
         <v>20500</v>
@@ -30417,10 +30417,10 @@
         <v>7</v>
       </c>
       <c r="N663" t="n">
-        <v>7605.4495327103</v>
+        <v>7465.9</v>
       </c>
       <c r="O663" t="n">
-        <v>53238.1467289721</v>
+        <v>52261.3</v>
       </c>
       <c r="P663" t="n">
         <v>11900</v>
@@ -30795,10 +30795,10 @@
         <v>13</v>
       </c>
       <c r="N671" t="n">
-        <v>44654.875337423</v>
+        <v>44113.604171779</v>
       </c>
       <c r="O671" t="n">
-        <v>580513.3793864991</v>
+        <v>573476.854233127</v>
       </c>
       <c r="P671" t="n">
         <v>71900</v>
@@ -31730,10 +31730,10 @@
         <v>56</v>
       </c>
       <c r="N691" t="n">
-        <v>5959.9565217391</v>
+        <v>5077</v>
       </c>
       <c r="O691" t="n">
-        <v>333757.5652173896</v>
+        <v>284312</v>
       </c>
       <c r="P691" t="n">
         <v>8500</v>
@@ -31776,10 +31776,10 @@
         <v>30</v>
       </c>
       <c r="N692" t="n">
-        <v>2098.7012987013</v>
+        <v>1600</v>
       </c>
       <c r="O692" t="n">
-        <v>62961.038961039</v>
+        <v>48000</v>
       </c>
       <c r="P692" t="n">
         <v>3500</v>
@@ -31822,10 +31822,10 @@
         <v>518</v>
       </c>
       <c r="N693" t="n">
-        <v>707.69883076923</v>
+        <v>705.5279692307701</v>
       </c>
       <c r="O693" t="n">
-        <v>366587.9943384611</v>
+        <v>365463.4880615389</v>
       </c>
       <c r="P693" t="n">
         <v>1500</v>
@@ -32561,10 +32561,10 @@
         <v>101</v>
       </c>
       <c r="N709" t="n">
-        <v>7342.5742574257</v>
+        <v>7200</v>
       </c>
       <c r="O709" t="n">
-        <v>741599.9999999957</v>
+        <v>727200</v>
       </c>
       <c r="P709" t="n">
         <v>8900</v>
@@ -32607,10 +32607,10 @@
         <v>40</v>
       </c>
       <c r="N710" t="n">
-        <v>14175</v>
+        <v>13500</v>
       </c>
       <c r="O710" t="n">
-        <v>567000</v>
+        <v>540000</v>
       </c>
       <c r="P710" t="n">
         <v>16900</v>
@@ -32653,10 +32653,10 @@
         <v>29</v>
       </c>
       <c r="N711" t="n">
-        <v>11544.827586207</v>
+        <v>10800</v>
       </c>
       <c r="O711" t="n">
-        <v>334800.000000003</v>
+        <v>313200</v>
       </c>
       <c r="P711" t="n">
         <v>13500</v>
@@ -32975,10 +32975,10 @@
         <v>19</v>
       </c>
       <c r="N718" t="n">
-        <v>2655.5149832776</v>
+        <v>2644.9</v>
       </c>
       <c r="O718" t="n">
-        <v>50454.7846822744</v>
+        <v>50253.1</v>
       </c>
       <c r="P718" t="n">
         <v>3900</v>
@@ -33251,10 +33251,10 @@
         <v>90</v>
       </c>
       <c r="N724" t="n">
-        <v>15731.466666667</v>
+        <v>15224</v>
       </c>
       <c r="O724" t="n">
-        <v>1415832.00000003</v>
+        <v>1370160</v>
       </c>
       <c r="P724" t="n">
         <v>19000</v>
@@ -33297,10 +33297,10 @@
         <v>89</v>
       </c>
       <c r="N725" t="n">
-        <v>15737.168539326</v>
+        <v>15224</v>
       </c>
       <c r="O725" t="n">
-        <v>1400608.000000014</v>
+        <v>1354936</v>
       </c>
       <c r="P725" t="n">
         <v>19000</v>
@@ -33573,10 +33573,10 @@
         <v>194</v>
       </c>
       <c r="N731" t="n">
-        <v>4111.5051546392</v>
+        <v>3872</v>
       </c>
       <c r="O731" t="n">
-        <v>797632.0000000048</v>
+        <v>751168</v>
       </c>
       <c r="P731" t="n">
         <v>4900</v>
@@ -33665,10 +33665,10 @@
         <v>234</v>
       </c>
       <c r="N733" t="n">
-        <v>4070.5641025641</v>
+        <v>3872</v>
       </c>
       <c r="O733" t="n">
-        <v>952511.9999999993</v>
+        <v>906048</v>
       </c>
       <c r="P733" t="n">
         <v>4900</v>
@@ -33895,10 +33895,10 @@
         <v>283</v>
       </c>
       <c r="N738" t="n">
-        <v>3485.7950530035</v>
+        <v>3344</v>
       </c>
       <c r="O738" t="n">
-        <v>986479.9999999905</v>
+        <v>946352</v>
       </c>
       <c r="P738" t="n">
         <v>4500</v>
@@ -34505,10 +34505,10 @@
         <v>13</v>
       </c>
       <c r="N751" t="n">
-        <v>6162.2222222222</v>
+        <v>5900</v>
       </c>
       <c r="O751" t="n">
-        <v>80108.8888888886</v>
+        <v>76700</v>
       </c>
       <c r="P751" t="n">
         <v>7100</v>
@@ -34597,10 +34597,10 @@
         <v>8</v>
       </c>
       <c r="N753" t="n">
-        <v>26102.941176471</v>
+        <v>25000</v>
       </c>
       <c r="O753" t="n">
-        <v>208823.529411768</v>
+        <v>200000</v>
       </c>
       <c r="P753" t="n">
         <v>30000</v>
@@ -35149,10 +35149,10 @@
         <v>10</v>
       </c>
       <c r="N765" t="n">
-        <v>6250</v>
+        <v>6000</v>
       </c>
       <c r="O765" t="n">
-        <v>62500</v>
+        <v>60000</v>
       </c>
       <c r="P765" t="n">
         <v>7200</v>
@@ -35614,10 +35614,10 @@
         <v>46</v>
       </c>
       <c r="N775" t="n">
-        <v>1494.6085714286</v>
+        <v>1482.84</v>
       </c>
       <c r="O775" t="n">
-        <v>68751.9942857156</v>
+        <v>68210.64</v>
       </c>
       <c r="P775" t="n">
         <v>6500</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -6210,10 +6210,10 @@
         <v>41</v>
       </c>
       <c r="N136" t="n">
-        <v>10899.560863636</v>
+        <v>10752.93</v>
       </c>
       <c r="O136" t="n">
-        <v>446881.995409076</v>
+        <v>440870.13</v>
       </c>
       <c r="P136" t="n">
         <v>18400</v>
@@ -6917,10 +6917,10 @@
         <v>38</v>
       </c>
       <c r="N152" t="n">
-        <v>13609.886922141</v>
+        <v>13593.35</v>
       </c>
       <c r="O152" t="n">
-        <v>517175.703041358</v>
+        <v>516547.3</v>
       </c>
       <c r="P152" t="n">
         <v>25500</v>
@@ -7181,10 +7181,10 @@
         <v>179</v>
       </c>
       <c r="N158" t="n">
-        <v>2583.5545646704</v>
+        <v>2582.2549874182</v>
       </c>
       <c r="O158" t="n">
-        <v>462456.2670760016</v>
+        <v>462223.6427478578</v>
       </c>
       <c r="P158" t="n">
         <v>4500</v>
@@ -7319,10 +7319,10 @@
         <v>637</v>
       </c>
       <c r="N161" t="n">
-        <v>3160.7464443118</v>
+        <v>3158.8608391782</v>
       </c>
       <c r="O161" t="n">
-        <v>2013395.485026617</v>
+        <v>2012194.354556513</v>
       </c>
       <c r="P161" t="n">
         <v>5600</v>
@@ -9543,10 +9543,10 @@
         <v>61</v>
       </c>
       <c r="N210" t="n">
-        <v>4372.0654674395</v>
+        <v>4371.1712628708</v>
       </c>
       <c r="O210" t="n">
-        <v>266695.9935138095</v>
+        <v>266641.4470351188</v>
       </c>
       <c r="P210" t="n">
         <v>8900</v>
@@ -10632,10 +10632,10 @@
         <v>2</v>
       </c>
       <c r="N234" t="n">
-        <v>3776.2176165803</v>
+        <v>3761.6</v>
       </c>
       <c r="O234" t="n">
-        <v>7552.4352331606</v>
+        <v>7523.2</v>
       </c>
       <c r="P234" t="n">
         <v>6900</v>
@@ -11032,10 +11032,10 @@
         <v>42</v>
       </c>
       <c r="N243" t="n">
-        <v>19114.611111111</v>
+        <v>18598</v>
       </c>
       <c r="O243" t="n">
-        <v>802813.666666662</v>
+        <v>781116</v>
       </c>
       <c r="P243" t="n">
         <v>21900</v>
@@ -11834,10 +11834,10 @@
         <v>1</v>
       </c>
       <c r="N261" t="n">
-        <v>7719.830483871</v>
+        <v>7537.4723387097</v>
       </c>
       <c r="O261" t="n">
-        <v>7719.830483871</v>
+        <v>7537.4723387097</v>
       </c>
       <c r="P261" t="n">
         <v>8900</v>
@@ -11875,10 +11875,10 @@
         <v>39</v>
       </c>
       <c r="N262" t="n">
-        <v>8799.4655328798</v>
+        <v>8794.48</v>
       </c>
       <c r="O262" t="n">
-        <v>343179.1557823122</v>
+        <v>342984.72</v>
       </c>
       <c r="P262" t="n">
         <v>14500</v>
@@ -12564,10 +12564,10 @@
         <v>17</v>
       </c>
       <c r="N278" t="n">
-        <v>57801.91954023</v>
+        <v>56503</v>
       </c>
       <c r="O278" t="n">
-        <v>982632.63218391</v>
+        <v>960551</v>
       </c>
       <c r="P278" t="n">
         <v>90500</v>
@@ -13414,10 +13414,10 @@
         <v>13</v>
       </c>
       <c r="N297" t="n">
-        <v>22761.155411606</v>
+        <v>22730.48</v>
       </c>
       <c r="O297" t="n">
-        <v>295895.020350878</v>
+        <v>295496.24</v>
       </c>
       <c r="P297" t="n">
         <v>36900</v>
@@ -13808,10 +13808,10 @@
         <v>83</v>
       </c>
       <c r="N306" t="n">
-        <v>4102.8563673709</v>
+        <v>4100.45</v>
       </c>
       <c r="O306" t="n">
-        <v>340537.0784917847</v>
+        <v>340337.35</v>
       </c>
       <c r="P306" t="n">
         <v>26900</v>
@@ -13941,10 +13941,10 @@
         <v>46</v>
       </c>
       <c r="N309" t="n">
-        <v>5455.0456387665</v>
+        <v>5431.12</v>
       </c>
       <c r="O309" t="n">
-        <v>250932.099383259</v>
+        <v>249831.52</v>
       </c>
       <c r="P309" t="n">
         <v>8900</v>
@@ -15672,10 +15672,10 @@
         <v>20</v>
       </c>
       <c r="N347" t="n">
-        <v>9252.7923611111</v>
+        <v>9188.98</v>
       </c>
       <c r="O347" t="n">
-        <v>185055.847222222</v>
+        <v>183779.6</v>
       </c>
       <c r="P347" t="n">
         <v>12900</v>
@@ -16270,10 +16270,10 @@
         <v>90</v>
       </c>
       <c r="N360" t="n">
-        <v>18023.2064</v>
+        <v>18016</v>
       </c>
       <c r="O360" t="n">
-        <v>1622088.576</v>
+        <v>1621440</v>
       </c>
       <c r="P360" t="n">
         <v>29900</v>
@@ -18311,10 +18311,10 @@
         <v>22</v>
       </c>
       <c r="N404" t="n">
-        <v>10448.584837545</v>
+        <v>10411</v>
       </c>
       <c r="O404" t="n">
-        <v>229868.86642599</v>
+        <v>229042</v>
       </c>
       <c r="P404" t="n">
         <v>16900</v>
@@ -21473,10 +21473,10 @@
         <v>27</v>
       </c>
       <c r="N473" t="n">
-        <v>60093.865363735</v>
+        <v>59834</v>
       </c>
       <c r="O473" t="n">
-        <v>1622534.364820845</v>
+        <v>1615518</v>
       </c>
       <c r="P473" t="n">
         <v>7900</v>
@@ -22028,10 +22028,10 @@
         <v>101</v>
       </c>
       <c r="N485" t="n">
-        <v>40318.846625767</v>
+        <v>40073</v>
       </c>
       <c r="O485" t="n">
-        <v>4072203.509202467</v>
+        <v>4047373</v>
       </c>
       <c r="P485" t="n">
         <v>64900</v>
@@ -22258,10 +22258,10 @@
         <v>49</v>
       </c>
       <c r="N490" t="n">
-        <v>3652.664695122</v>
+        <v>3639.35</v>
       </c>
       <c r="O490" t="n">
-        <v>178980.570060978</v>
+        <v>178328.15</v>
       </c>
       <c r="P490" t="n">
         <v>7500</v>
@@ -23135,10 +23135,10 @@
         <v>371</v>
       </c>
       <c r="N509" t="n">
-        <v>2463.8091310592</v>
+        <v>2458.5124991023</v>
       </c>
       <c r="O509" t="n">
-        <v>914073.1876229632</v>
+        <v>912108.1371669533</v>
       </c>
       <c r="P509" t="n">
         <v>3500</v>
@@ -25362,10 +25362,10 @@
         <v>116</v>
       </c>
       <c r="N557" t="n">
-        <v>345.63428985635</v>
+        <v>345.55838597724</v>
       </c>
       <c r="O557" t="n">
-        <v>40093.5776233366</v>
+        <v>40084.77277335984</v>
       </c>
       <c r="P557" t="n">
         <v>600</v>
@@ -25504,10 +25504,10 @@
         <v>86</v>
       </c>
       <c r="N560" t="n">
-        <v>711.87861852814</v>
+        <v>711.33664519481</v>
       </c>
       <c r="O560" t="n">
-        <v>61221.56119342004</v>
+        <v>61174.95148675366</v>
       </c>
       <c r="P560" t="n">
         <v>900</v>
@@ -29087,10 +29087,10 @@
         <v>105</v>
       </c>
       <c r="N635" t="n">
-        <v>3503.9263942308</v>
+        <v>3499.72</v>
       </c>
       <c r="O635" t="n">
-        <v>367912.271394234</v>
+        <v>367470.6</v>
       </c>
       <c r="P635" t="n">
         <v>6900</v>
@@ -29136,10 +29136,10 @@
         <v>109</v>
       </c>
       <c r="N636" t="n">
-        <v>5370.7341880342</v>
+        <v>5347.88</v>
       </c>
       <c r="O636" t="n">
-        <v>585410.0264957278</v>
+        <v>582918.92</v>
       </c>
       <c r="P636" t="n">
         <v>7900</v>
@@ -29185,10 +29185,10 @@
         <v>114</v>
       </c>
       <c r="N637" t="n">
-        <v>4593.2494352159</v>
+        <v>4578.04</v>
       </c>
       <c r="O637" t="n">
-        <v>523630.4356146126</v>
+        <v>521896.56</v>
       </c>
       <c r="P637" t="n">
         <v>7500</v>
@@ -30657,10 +30657,10 @@
         <v>314</v>
       </c>
       <c r="N668" t="n">
-        <v>7056.0857581657</v>
+        <v>7046.9398269522</v>
       </c>
       <c r="O668" t="n">
-        <v>2215610.92806403</v>
+        <v>2212739.105662991</v>
       </c>
       <c r="P668" t="n">
         <v>9900</v>
@@ -33257,10 +33257,10 @@
         <v>432</v>
       </c>
       <c r="N724" t="n">
-        <v>7496.4757709251</v>
+        <v>7480</v>
       </c>
       <c r="O724" t="n">
-        <v>3238477.533039643</v>
+        <v>3231360</v>
       </c>
       <c r="P724" t="n">
         <v>9500</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-20</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-21</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -950,10 +950,10 @@
         <v>73</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3093916756</v>
+        <v>1830.8488673139</v>
       </c>
       <c r="O13" t="n">
-        <v>132225.5855923188</v>
+        <v>133651.9673139147</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -3142,10 +3142,10 @@
         <v>21</v>
       </c>
       <c r="N65" t="n">
-        <v>9392.0756666667</v>
+        <v>9392.075964912299</v>
       </c>
       <c r="O65" t="n">
-        <v>197233.5890000007</v>
+        <v>197233.5952631583</v>
       </c>
       <c r="P65" t="n">
         <v>18500</v>
@@ -6555,22 +6555,22 @@
         <v>0</v>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M144" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N144" t="n">
         <v>3775.99</v>
       </c>
       <c r="O144" t="n">
-        <v>158591.58</v>
+        <v>151039.6</v>
       </c>
       <c r="P144" t="n">
         <v>7300</v>
       </c>
       <c r="Q144" t="n">
-        <v>306600</v>
+        <v>292000</v>
       </c>
     </row>
     <row r="145">
@@ -7181,10 +7181,10 @@
         <v>178</v>
       </c>
       <c r="N158" t="n">
-        <v>2582.2549620637</v>
+        <v>2582.2549607893</v>
       </c>
       <c r="O158" t="n">
-        <v>459641.3832473386</v>
+        <v>459641.3830204954</v>
       </c>
       <c r="P158" t="n">
         <v>4500</v>
@@ -7273,10 +7273,10 @@
         <v>43</v>
       </c>
       <c r="N160" t="n">
-        <v>5216.8958877086</v>
+        <v>5216.8958858357</v>
       </c>
       <c r="O160" t="n">
-        <v>224326.5231714698</v>
+        <v>224326.5230909351</v>
       </c>
       <c r="P160" t="n">
         <v>8500</v>
@@ -7319,10 +7319,10 @@
         <v>637</v>
       </c>
       <c r="N161" t="n">
-        <v>3158.8608391782</v>
+        <v>3158.86083922</v>
       </c>
       <c r="O161" t="n">
-        <v>2012194.354556513</v>
+        <v>2012194.35458314</v>
       </c>
       <c r="P161" t="n">
         <v>5600</v>
@@ -7733,10 +7733,10 @@
         <v>168</v>
       </c>
       <c r="N170" t="n">
-        <v>3795.7100076176</v>
+        <v>3795.7100076234</v>
       </c>
       <c r="O170" t="n">
-        <v>637679.2812797568</v>
+        <v>637679.2812807312</v>
       </c>
       <c r="P170" t="n">
         <v>6200</v>
@@ -7958,10 +7958,10 @@
         <v>50</v>
       </c>
       <c r="N175" t="n">
-        <v>4890.9300534045</v>
+        <v>4890.9300534402</v>
       </c>
       <c r="O175" t="n">
-        <v>244546.502670225</v>
+        <v>244546.50267201</v>
       </c>
       <c r="P175" t="n">
         <v>8200</v>
@@ -8273,10 +8273,10 @@
         <v>82</v>
       </c>
       <c r="N182" t="n">
-        <v>2267.0480923608</v>
+        <v>2267.0480857514</v>
       </c>
       <c r="O182" t="n">
-        <v>185897.9435735856</v>
+        <v>185897.9430316148</v>
       </c>
       <c r="P182" t="n">
         <v>3900</v>
@@ -8634,10 +8634,10 @@
         <v>40</v>
       </c>
       <c r="N190" t="n">
-        <v>3594.2530181818</v>
+        <v>3594.2529978118</v>
       </c>
       <c r="O190" t="n">
-        <v>143770.120727272</v>
+        <v>143770.119912472</v>
       </c>
       <c r="P190" t="n">
         <v>6500</v>
@@ -8723,22 +8723,22 @@
         <v>0</v>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M192" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="N192" t="n">
         <v>489.88</v>
       </c>
       <c r="O192" t="n">
-        <v>591285.16</v>
+        <v>579528.04</v>
       </c>
       <c r="P192" t="n">
         <v>700</v>
       </c>
       <c r="Q192" t="n">
-        <v>844900</v>
+        <v>828100</v>
       </c>
     </row>
     <row r="193">
@@ -9497,10 +9497,10 @@
         <v>116</v>
       </c>
       <c r="N209" t="n">
-        <v>3041.6600141844</v>
+        <v>3041.6600141945</v>
       </c>
       <c r="O209" t="n">
-        <v>352832.5616453904</v>
+        <v>352832.561646562</v>
       </c>
       <c r="P209" t="n">
         <v>5500</v>
@@ -9543,10 +9543,10 @@
         <v>61</v>
       </c>
       <c r="N210" t="n">
-        <v>4371.1712629569</v>
+        <v>4371.7675214841</v>
       </c>
       <c r="O210" t="n">
-        <v>266641.4470403709</v>
+        <v>266677.8188105301</v>
       </c>
       <c r="P210" t="n">
         <v>8900</v>
@@ -9899,10 +9899,10 @@
         <v>284</v>
       </c>
       <c r="N218" t="n">
-        <v>4648.6</v>
+        <v>4649.4131187686</v>
       </c>
       <c r="O218" t="n">
-        <v>1320202.4</v>
+        <v>1320433.325730282</v>
       </c>
       <c r="P218" t="n">
         <v>8900</v>
@@ -10898,22 +10898,22 @@
         <v>0</v>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M240" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N240" t="n">
-        <v>2403.5202775057</v>
+        <v>2407.4618268285</v>
       </c>
       <c r="O240" t="n">
-        <v>64895.0474926539</v>
+        <v>55371.6220170555</v>
       </c>
       <c r="P240" t="n">
         <v>3500</v>
       </c>
       <c r="Q240" t="n">
-        <v>94500</v>
+        <v>80500</v>
       </c>
     </row>
     <row r="241">
@@ -12003,10 +12003,10 @@
         <v>118</v>
       </c>
       <c r="N265" t="n">
-        <v>2517.22</v>
+        <v>2545.636406397</v>
       </c>
       <c r="O265" t="n">
-        <v>297031.96</v>
+        <v>300385.095954846</v>
       </c>
       <c r="P265" t="n">
         <v>4200</v>
@@ -12298,10 +12298,10 @@
         <v>4</v>
       </c>
       <c r="N272" t="n">
-        <v>24538.02</v>
+        <v>25442.647465438</v>
       </c>
       <c r="O272" t="n">
-        <v>98152.08</v>
+        <v>101770.589861752</v>
       </c>
       <c r="P272" t="n">
         <v>52900</v>
@@ -12599,22 +12599,22 @@
         <v>0</v>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M279" t="n">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="N279" t="n">
         <v>1651</v>
       </c>
       <c r="O279" t="n">
-        <v>751205</v>
+        <v>744601</v>
       </c>
       <c r="P279" t="n">
         <v>2500</v>
       </c>
       <c r="Q279" t="n">
-        <v>1137500</v>
+        <v>1127500</v>
       </c>
     </row>
     <row r="280">
@@ -12746,10 +12746,10 @@
         <v>76</v>
       </c>
       <c r="N282" t="n">
-        <v>4285.1963420724</v>
+        <v>4285.1963819095</v>
       </c>
       <c r="O282" t="n">
-        <v>325674.9219975024</v>
+        <v>325674.925025122</v>
       </c>
       <c r="P282" t="n">
         <v>6900</v>
@@ -13808,10 +13808,10 @@
         <v>83</v>
       </c>
       <c r="N306" t="n">
-        <v>4100.45</v>
+        <v>4107.6818342152</v>
       </c>
       <c r="O306" t="n">
-        <v>340337.35</v>
+        <v>340937.5922398616</v>
       </c>
       <c r="P306" t="n">
         <v>26900</v>
@@ -13854,10 +13854,10 @@
         <v>14</v>
       </c>
       <c r="N307" t="n">
-        <v>8332.779612403099</v>
+        <v>8332.7796073298</v>
       </c>
       <c r="O307" t="n">
-        <v>116658.9145736434</v>
+        <v>116658.9145026172</v>
       </c>
       <c r="P307" t="n">
         <v>14900</v>
@@ -13987,10 +13987,10 @@
         <v>552</v>
       </c>
       <c r="N310" t="n">
-        <v>1561.0051173709</v>
+        <v>1600.4118322476</v>
       </c>
       <c r="O310" t="n">
-        <v>861674.8247887369</v>
+        <v>883427.3314006751</v>
       </c>
       <c r="P310" t="n">
         <v>2900</v>
@@ -14291,22 +14291,22 @@
         <v>0</v>
       </c>
       <c r="L317" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M317" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N317" t="n">
-        <v>7969.9501704105</v>
+        <v>7969.9501706749</v>
       </c>
       <c r="O317" t="n">
-        <v>1099853.123516649</v>
+        <v>1083913.223211786</v>
       </c>
       <c r="P317" t="n">
         <v>12900</v>
       </c>
       <c r="Q317" t="n">
-        <v>1780200</v>
+        <v>1754400</v>
       </c>
     </row>
     <row r="318">
@@ -14515,10 +14515,10 @@
         <v>22</v>
       </c>
       <c r="N322" t="n">
-        <v>548.14707537688</v>
+        <v>548.1470665322601</v>
       </c>
       <c r="O322" t="n">
-        <v>12059.23565829136</v>
+        <v>12059.23546370972</v>
       </c>
       <c r="P322" t="n">
         <v>2000</v>
@@ -16178,10 +16178,10 @@
         <v>39</v>
       </c>
       <c r="N358" t="n">
-        <v>1778.4728413344</v>
+        <v>1778.4728487518</v>
       </c>
       <c r="O358" t="n">
-        <v>69360.4408120416</v>
+        <v>69360.4411013202</v>
       </c>
       <c r="P358" t="n">
         <v>4900</v>
@@ -18495,10 +18495,10 @@
         <v>20</v>
       </c>
       <c r="N408" t="n">
-        <v>2252.298328125</v>
+        <v>2252.2983673469</v>
       </c>
       <c r="O408" t="n">
-        <v>45045.9665625</v>
+        <v>45045.96734693799</v>
       </c>
       <c r="P408" t="n">
         <v>3900</v>
@@ -19280,10 +19280,10 @@
         <v>41</v>
       </c>
       <c r="N425" t="n">
-        <v>6414</v>
+        <v>6426.9445005045</v>
       </c>
       <c r="O425" t="n">
-        <v>262974</v>
+        <v>263504.7245206845</v>
       </c>
       <c r="P425" t="n">
         <v>10900</v>
@@ -19602,10 +19602,10 @@
         <v>226</v>
       </c>
       <c r="N432" t="n">
-        <v>3903.7394479074</v>
+        <v>3903.7394652406</v>
       </c>
       <c r="O432" t="n">
-        <v>882245.1152270724</v>
+        <v>882245.1191443757</v>
       </c>
       <c r="P432" t="n">
         <v>7500</v>
@@ -19954,22 +19954,22 @@
         <v>0</v>
       </c>
       <c r="L440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M440" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N440" t="n">
         <v>4202</v>
       </c>
       <c r="O440" t="n">
-        <v>130262</v>
+        <v>126060</v>
       </c>
       <c r="P440" t="n">
         <v>7900</v>
       </c>
       <c r="Q440" t="n">
-        <v>244900</v>
+        <v>237000</v>
       </c>
     </row>
     <row r="441">
@@ -20420,10 +20420,10 @@
         <v>99</v>
       </c>
       <c r="N450" t="n">
-        <v>6645</v>
+        <v>6648.7102177554</v>
       </c>
       <c r="O450" t="n">
-        <v>657855</v>
+        <v>658222.3115577846</v>
       </c>
       <c r="P450" t="n">
         <v>10900</v>
@@ -20650,10 +20650,10 @@
         <v>134</v>
       </c>
       <c r="N455" t="n">
-        <v>3898</v>
+        <v>3904.464344942</v>
       </c>
       <c r="O455" t="n">
-        <v>522332</v>
+        <v>523198.222222228</v>
       </c>
       <c r="P455" t="n">
         <v>6900</v>
@@ -21196,22 +21196,22 @@
         <v>0</v>
       </c>
       <c r="L467" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M467" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N467" t="n">
         <v>11348</v>
       </c>
       <c r="O467" t="n">
-        <v>147524</v>
+        <v>124828</v>
       </c>
       <c r="P467" t="n">
         <v>19900</v>
       </c>
       <c r="Q467" t="n">
-        <v>258700</v>
+        <v>218900</v>
       </c>
     </row>
     <row r="468">
@@ -23135,10 +23135,10 @@
         <v>371</v>
       </c>
       <c r="N509" t="n">
-        <v>2458.5124311594</v>
+        <v>2458.5124201742</v>
       </c>
       <c r="O509" t="n">
-        <v>912108.1119601374</v>
+        <v>912108.1078846282</v>
       </c>
       <c r="P509" t="n">
         <v>3500</v>
@@ -23181,10 +23181,10 @@
         <v>140</v>
       </c>
       <c r="N510" t="n">
-        <v>1771.0893441415</v>
+        <v>1771.0893205318</v>
       </c>
       <c r="O510" t="n">
-        <v>247952.50817981</v>
+        <v>247952.504874452</v>
       </c>
       <c r="P510" t="n">
         <v>2500</v>
@@ -23273,10 +23273,10 @@
         <v>109</v>
       </c>
       <c r="N512" t="n">
-        <v>1803.0169781803</v>
+        <v>1803.0169868096</v>
       </c>
       <c r="O512" t="n">
-        <v>196528.8506216527</v>
+        <v>196528.8515622464</v>
       </c>
       <c r="P512" t="n">
         <v>2500</v>
@@ -23725,22 +23725,22 @@
         <v>0</v>
       </c>
       <c r="L522" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M522" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N522" t="n">
         <v>5347.73</v>
       </c>
       <c r="O522" t="n">
-        <v>192518.28</v>
+        <v>187170.55</v>
       </c>
       <c r="P522" t="n">
         <v>9500</v>
       </c>
       <c r="Q522" t="n">
-        <v>342000</v>
+        <v>332500</v>
       </c>
     </row>
     <row r="523">
@@ -23823,10 +23823,10 @@
         <v>841</v>
       </c>
       <c r="N524" t="n">
-        <v>1259.2749291992</v>
+        <v>1262.9750514202</v>
       </c>
       <c r="O524" t="n">
-        <v>1059050.215456527</v>
+        <v>1062162.018244388</v>
       </c>
       <c r="P524" t="n">
         <v>1900</v>
@@ -24723,10 +24723,10 @@
         <v>227</v>
       </c>
       <c r="N543" t="n">
-        <v>1530.4499180664</v>
+        <v>1538.0108069164</v>
       </c>
       <c r="O543" t="n">
-        <v>347412.1314010728</v>
+        <v>349128.4531700228</v>
       </c>
       <c r="P543" t="n">
         <v>2600</v>
@@ -26062,10 +26062,10 @@
         <v>133</v>
       </c>
       <c r="N572" t="n">
-        <v>517.2950312417501</v>
+        <v>517.29511103247</v>
       </c>
       <c r="O572" t="n">
-        <v>68800.23915515275</v>
+        <v>68800.24976731851</v>
       </c>
       <c r="P572" t="n">
         <v>900</v>
@@ -26247,10 +26247,10 @@
         <v>299</v>
       </c>
       <c r="N576" t="n">
-        <v>703.7947376286299</v>
+        <v>703.79473431536</v>
       </c>
       <c r="O576" t="n">
-        <v>210434.6265509604</v>
+        <v>210434.6255602926</v>
       </c>
       <c r="P576" t="n">
         <v>900</v>
@@ -29702,10 +29702,10 @@
         <v>8</v>
       </c>
       <c r="N648" t="n">
-        <v>10737.525714286</v>
+        <v>10737.525609756</v>
       </c>
       <c r="O648" t="n">
-        <v>85900.20571428799</v>
+        <v>85900.204878048</v>
       </c>
       <c r="P648" t="n">
         <v>18900</v>
@@ -30651,22 +30651,22 @@
         <v>0</v>
       </c>
       <c r="L668" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M668" t="n">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="N668" t="n">
         <v>509.69</v>
       </c>
       <c r="O668" t="n">
-        <v>269626.01</v>
+        <v>264529.11</v>
       </c>
       <c r="P668" t="n">
         <v>750</v>
       </c>
       <c r="Q668" t="n">
-        <v>396750</v>
+        <v>389250</v>
       </c>
     </row>
     <row r="669">
@@ -30890,22 +30890,22 @@
         <v>0</v>
       </c>
       <c r="L673" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M673" t="n">
-        <v>450</v>
+        <v>410</v>
       </c>
       <c r="N673" t="n">
         <v>796.3099999999999</v>
       </c>
       <c r="O673" t="n">
-        <v>358339.5</v>
+        <v>326487.1</v>
       </c>
       <c r="P673" t="n">
         <v>2500</v>
       </c>
       <c r="Q673" t="n">
-        <v>1125000</v>
+        <v>1025000</v>
       </c>
     </row>
     <row r="674">
@@ -32656,22 +32656,22 @@
         <v>0</v>
       </c>
       <c r="L711" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M711" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="N711" t="n">
         <v>13500</v>
       </c>
       <c r="O711" t="n">
-        <v>445500</v>
+        <v>405000</v>
       </c>
       <c r="P711" t="n">
         <v>16900</v>
       </c>
       <c r="Q711" t="n">
-        <v>557700</v>
+        <v>507000</v>
       </c>
     </row>
     <row r="712">
@@ -33996,10 +33996,10 @@
         <v>555</v>
       </c>
       <c r="N740" t="n">
-        <v>6160</v>
+        <v>6202.5414364641</v>
       </c>
       <c r="O740" t="n">
-        <v>3418800</v>
+        <v>3442410.497237576</v>
       </c>
       <c r="P740" t="n">
         <v>7500</v>
@@ -34223,22 +34223,22 @@
         <v>0</v>
       </c>
       <c r="L745" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M745" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="N745" t="n">
         <v>7216</v>
       </c>
       <c r="O745" t="n">
-        <v>303072</v>
+        <v>274208</v>
       </c>
       <c r="P745" t="n">
         <v>9000</v>
       </c>
       <c r="Q745" t="n">
-        <v>378000</v>
+        <v>342000</v>
       </c>
     </row>
     <row r="746">
@@ -36359,22 +36359,22 @@
         <v>0</v>
       </c>
       <c r="L791" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M791" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N791" t="n">
         <v>4550</v>
       </c>
       <c r="O791" t="n">
-        <v>964600</v>
+        <v>955500</v>
       </c>
       <c r="P791" t="n">
         <v>5500</v>
       </c>
       <c r="Q791" t="n">
-        <v>1166000</v>
+        <v>1155000</v>
       </c>
     </row>
     <row r="792">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -9188,10 +9188,10 @@
         <v>51</v>
       </c>
       <c r="N202" t="n">
-        <v>12422.462959583</v>
+        <v>12422.46296087</v>
       </c>
       <c r="O202" t="n">
-        <v>633545.610938733</v>
+        <v>633545.61100437</v>
       </c>
       <c r="P202" t="n">
         <v>19900</v>
@@ -10904,10 +10904,10 @@
         <v>19</v>
       </c>
       <c r="N240" t="n">
-        <v>2403.5207171448</v>
+        <v>2403.5207309746</v>
       </c>
       <c r="O240" t="n">
-        <v>45666.8936257512</v>
+        <v>45666.8938885174</v>
       </c>
       <c r="P240" t="n">
         <v>3500</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -1864,10 +1864,10 @@
         <v>57</v>
       </c>
       <c r="N36" t="n">
-        <v>3716.3301967213</v>
+        <v>3716.3301970443</v>
       </c>
       <c r="O36" t="n">
-        <v>211830.8212131141</v>
+        <v>211830.8212315251</v>
       </c>
       <c r="P36" t="n">
         <v>9500</v>
@@ -8634,10 +8634,10 @@
         <v>40</v>
       </c>
       <c r="N190" t="n">
-        <v>3594.2529307806</v>
+        <v>3594.2529255711</v>
       </c>
       <c r="O190" t="n">
-        <v>143770.117231224</v>
+        <v>143770.117022844</v>
       </c>
       <c r="P190" t="n">
         <v>6500</v>
@@ -9188,10 +9188,10 @@
         <v>51</v>
       </c>
       <c r="N202" t="n">
-        <v>12422.462986842</v>
+        <v>12422.462990777</v>
       </c>
       <c r="O202" t="n">
-        <v>633545.6123289419</v>
+        <v>633545.6125296269</v>
       </c>
       <c r="P202" t="n">
         <v>19900</v>
@@ -9543,10 +9543,10 @@
         <v>116</v>
       </c>
       <c r="N210" t="n">
-        <v>3041.6600148258</v>
+        <v>3041.6600148478</v>
       </c>
       <c r="O210" t="n">
-        <v>352832.5617197928</v>
+        <v>352832.5617223448</v>
       </c>
       <c r="P210" t="n">
         <v>5500</v>
@@ -12789,10 +12789,10 @@
         <v>76</v>
       </c>
       <c r="N283" t="n">
-        <v>4285.1964141414</v>
+        <v>4285.1964303797</v>
       </c>
       <c r="O283" t="n">
-        <v>325674.9274747464</v>
+        <v>325674.9287088572</v>
       </c>
       <c r="P283" t="n">
         <v>6900</v>
@@ -23040,10 +23040,10 @@
         <v>313</v>
       </c>
       <c r="N507" t="n">
-        <v>1516.0387356204</v>
+        <v>1516.0387309278</v>
       </c>
       <c r="O507" t="n">
-        <v>474520.1242491852</v>
+        <v>474520.1227804014</v>
       </c>
       <c r="P507" t="n">
         <v>2300</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -950,10 +950,10 @@
         <v>25</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3106796117</v>
+        <v>1811.3107843137</v>
       </c>
       <c r="O13" t="n">
-        <v>45282.7669902925</v>
+        <v>45282.7696078425</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -7359,22 +7359,22 @@
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M162" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="N162" t="n">
         <v>1480</v>
       </c>
       <c r="O162" t="n">
-        <v>395160</v>
+        <v>392200</v>
       </c>
       <c r="P162" t="n">
         <v>2600</v>
       </c>
       <c r="Q162" t="n">
-        <v>694200</v>
+        <v>689000</v>
       </c>
     </row>
     <row r="163">
@@ -7687,10 +7687,10 @@
         <v>164</v>
       </c>
       <c r="N169" t="n">
-        <v>3795.7100076321</v>
+        <v>3795.710007638</v>
       </c>
       <c r="O169" t="n">
-        <v>622496.4412516644</v>
+        <v>622496.4412526321</v>
       </c>
       <c r="P169" t="n">
         <v>6200</v>
@@ -7912,10 +7912,10 @@
         <v>45</v>
       </c>
       <c r="N174" t="n">
-        <v>4890.9300537634</v>
+        <v>4890.9300539811</v>
       </c>
       <c r="O174" t="n">
-        <v>220091.852419353</v>
+        <v>220091.8524291495</v>
       </c>
       <c r="P174" t="n">
         <v>8200</v>
@@ -8723,22 +8723,22 @@
         <v>0</v>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M192" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="N192" t="n">
-        <v>4891</v>
+        <v>4906.5393169182</v>
       </c>
       <c r="O192" t="n">
-        <v>200531</v>
+        <v>181541.9547259734</v>
       </c>
       <c r="P192" t="n">
         <v>8200</v>
       </c>
       <c r="Q192" t="n">
-        <v>336200</v>
+        <v>303400</v>
       </c>
     </row>
     <row r="193">
@@ -9313,22 +9313,22 @@
         <v>0</v>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M205" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="N205" t="n">
-        <v>3472.2762877567</v>
+        <v>3472.2762983503</v>
       </c>
       <c r="O205" t="n">
-        <v>187502.9195388618</v>
+        <v>125001.9467406108</v>
       </c>
       <c r="P205" t="n">
         <v>5900</v>
       </c>
       <c r="Q205" t="n">
-        <v>318600</v>
+        <v>212400</v>
       </c>
     </row>
     <row r="206">
@@ -9543,10 +9543,10 @@
         <v>58</v>
       </c>
       <c r="N210" t="n">
-        <v>4371.1712633877</v>
+        <v>4371.171263905</v>
       </c>
       <c r="O210" t="n">
-        <v>253527.9332764866</v>
+        <v>253527.93330649</v>
       </c>
       <c r="P210" t="n">
         <v>8900</v>
@@ -10208,22 +10208,22 @@
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M225" t="n">
-        <v>2097</v>
+        <v>2094</v>
       </c>
       <c r="N225" t="n">
         <v>1387.55</v>
       </c>
       <c r="O225" t="n">
-        <v>2909692.35</v>
+        <v>2905529.7</v>
       </c>
       <c r="P225" t="n">
         <v>2300</v>
       </c>
       <c r="Q225" t="n">
-        <v>4823100</v>
+        <v>4816200</v>
       </c>
     </row>
     <row r="226">
@@ -10855,10 +10855,10 @@
         <v>19</v>
       </c>
       <c r="N239" t="n">
-        <v>2403.5211979522</v>
+        <v>2403.5212124317</v>
       </c>
       <c r="O239" t="n">
-        <v>45666.9027610918</v>
+        <v>45666.9030362023</v>
       </c>
       <c r="P239" t="n">
         <v>3500</v>
@@ -12642,22 +12642,22 @@
         <v>0</v>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M280" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="N280" t="n">
-        <v>6207.9882231175</v>
+        <v>6213.167301168</v>
       </c>
       <c r="O280" t="n">
-        <v>372479.29338705</v>
+        <v>335511.034263072</v>
       </c>
       <c r="P280" t="n">
         <v>9900</v>
       </c>
       <c r="Q280" t="n">
-        <v>594000</v>
+        <v>534600</v>
       </c>
     </row>
     <row r="281">
@@ -13083,22 +13083,22 @@
         <v>0</v>
       </c>
       <c r="L290" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M290" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="N290" t="n">
-        <v>3591.13</v>
+        <v>3594.9639466192</v>
       </c>
       <c r="O290" t="n">
-        <v>280108.14</v>
+        <v>258837.4041565824</v>
       </c>
       <c r="P290" t="n">
         <v>6300</v>
       </c>
       <c r="Q290" t="n">
-        <v>491400</v>
+        <v>453600</v>
       </c>
     </row>
     <row r="291">
@@ -14416,22 +14416,22 @@
         <v>0</v>
       </c>
       <c r="L320" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M320" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="N320" t="n">
-        <v>9627.34</v>
+        <v>9808.987924528299</v>
       </c>
       <c r="O320" t="n">
-        <v>452484.98</v>
+        <v>431595.4686792452</v>
       </c>
       <c r="P320" t="n">
         <v>15900</v>
       </c>
       <c r="Q320" t="n">
-        <v>747300</v>
+        <v>699600</v>
       </c>
     </row>
     <row r="321">
@@ -14512,10 +14512,10 @@
         <v>22</v>
       </c>
       <c r="N322" t="n">
-        <v>548.14706357215</v>
+        <v>548.14704568528</v>
       </c>
       <c r="O322" t="n">
-        <v>12059.2353985873</v>
+        <v>12059.23500507616</v>
       </c>
       <c r="P322" t="n">
         <v>2000</v>
@@ -18164,22 +18164,22 @@
         <v>0</v>
       </c>
       <c r="L401" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M401" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="N401" t="n">
-        <v>8858.16</v>
+        <v>8873.1568848758</v>
       </c>
       <c r="O401" t="n">
-        <v>363184.56</v>
+        <v>337179.9616252804</v>
       </c>
       <c r="P401" t="n">
         <v>15500</v>
       </c>
       <c r="Q401" t="n">
-        <v>635500</v>
+        <v>589000</v>
       </c>
     </row>
     <row r="402">
@@ -20181,22 +20181,22 @@
         <v>0</v>
       </c>
       <c r="L445" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M445" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="N445" t="n">
-        <v>6849.2</v>
+        <v>6862.329456869</v>
       </c>
       <c r="O445" t="n">
-        <v>986284.7999999999</v>
+        <v>940139.1355910529</v>
       </c>
       <c r="P445" t="n">
         <v>11500</v>
       </c>
       <c r="Q445" t="n">
-        <v>1656000</v>
+        <v>1575500</v>
       </c>
     </row>
     <row r="446">
@@ -22948,10 +22948,10 @@
         <v>313</v>
       </c>
       <c r="N505" t="n">
-        <v>1516.0387272539</v>
+        <v>1516.0387269907</v>
       </c>
       <c r="O505" t="n">
-        <v>474520.1216304707</v>
+        <v>474520.1215480891</v>
       </c>
       <c r="P505" t="n">
         <v>2300</v>
@@ -23086,10 +23086,10 @@
         <v>140</v>
       </c>
       <c r="N508" t="n">
-        <v>1771.0893205318</v>
+        <v>1771.0891278195</v>
       </c>
       <c r="O508" t="n">
-        <v>247952.504874452</v>
+        <v>247952.47789473</v>
       </c>
       <c r="P508" t="n">
         <v>2500</v>
@@ -23408,10 +23408,10 @@
         <v>292</v>
       </c>
       <c r="N515" t="n">
-        <v>3224.5699223947</v>
+        <v>3224.5699334073</v>
       </c>
       <c r="O515" t="n">
-        <v>941574.4173392524</v>
+        <v>941574.4205549316</v>
       </c>
       <c r="P515" t="n">
         <v>4500</v>
@@ -23454,10 +23454,10 @@
         <v>230</v>
       </c>
       <c r="N516" t="n">
-        <v>1655.9291188041</v>
+        <v>1655.9290150913</v>
       </c>
       <c r="O516" t="n">
-        <v>380863.697324943</v>
+        <v>380863.673470999</v>
       </c>
       <c r="P516" t="n">
         <v>2500</v>
@@ -24238,22 +24238,22 @@
         <v>0</v>
       </c>
       <c r="L533" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M533" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="N533" t="n">
         <v>5215</v>
       </c>
       <c r="O533" t="n">
-        <v>260750</v>
+        <v>229460</v>
       </c>
       <c r="P533" t="n">
         <v>8900</v>
       </c>
       <c r="Q533" t="n">
-        <v>445000</v>
+        <v>391600</v>
       </c>
     </row>
     <row r="534">
@@ -24809,22 +24809,22 @@
         <v>0</v>
       </c>
       <c r="L545" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M545" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N545" t="n">
         <v>1245.62</v>
       </c>
       <c r="O545" t="n">
-        <v>124562</v>
+        <v>123316.38</v>
       </c>
       <c r="P545" t="n">
         <v>4000</v>
       </c>
       <c r="Q545" t="n">
-        <v>400000</v>
+        <v>396000</v>
       </c>
     </row>
     <row r="546">
@@ -26201,10 +26201,10 @@
         <v>171</v>
       </c>
       <c r="N575" t="n">
-        <v>703.79469605084</v>
+        <v>703.79468467395</v>
       </c>
       <c r="O575" t="n">
-        <v>120348.8930246936</v>
+        <v>120348.8910792454</v>
       </c>
       <c r="P575" t="n">
         <v>900</v>
@@ -31776,22 +31776,22 @@
         <v>0</v>
       </c>
       <c r="L692" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M692" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N692" t="n">
         <v>5077</v>
       </c>
       <c r="O692" t="n">
-        <v>213234</v>
+        <v>208157</v>
       </c>
       <c r="P692" t="n">
         <v>8500</v>
       </c>
       <c r="Q692" t="n">
-        <v>357000</v>
+        <v>348500</v>
       </c>
     </row>
     <row r="693">
@@ -33665,22 +33665,22 @@
         <v>0</v>
       </c>
       <c r="L733" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M733" t="n">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="N733" t="n">
         <v>3344</v>
       </c>
       <c r="O733" t="n">
-        <v>892848</v>
+        <v>852720</v>
       </c>
       <c r="P733" t="n">
         <v>4500</v>
       </c>
       <c r="Q733" t="n">
-        <v>1201500</v>
+        <v>1147500</v>
       </c>
     </row>
     <row r="734">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -1579,22 +1579,22 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N29" t="n">
-        <v>12357.960428571</v>
+        <v>12357.960431655</v>
       </c>
       <c r="O29" t="n">
-        <v>222443.287714278</v>
+        <v>210085.327338135</v>
       </c>
       <c r="P29" t="n">
         <v>15900</v>
       </c>
       <c r="Q29" t="n">
-        <v>286200</v>
+        <v>270300</v>
       </c>
     </row>
     <row r="30">
@@ -1942,10 +1942,10 @@
         <v>79</v>
       </c>
       <c r="N38" t="n">
-        <v>2785.6243902439</v>
+        <v>2681</v>
       </c>
       <c r="O38" t="n">
-        <v>220064.3268292681</v>
+        <v>211799</v>
       </c>
       <c r="P38" t="n">
         <v>3500</v>
@@ -3095,10 +3095,10 @@
         <v>39</v>
       </c>
       <c r="N64" t="n">
-        <v>15711.963831169</v>
+        <v>15711.96379085</v>
       </c>
       <c r="O64" t="n">
-        <v>612766.589415591</v>
+        <v>612766.58784315</v>
       </c>
       <c r="P64" t="n">
         <v>28500</v>
@@ -5195,10 +5195,10 @@
         <v>40</v>
       </c>
       <c r="N113" t="n">
-        <v>2584.1380683507</v>
+        <v>2572.67</v>
       </c>
       <c r="O113" t="n">
-        <v>103365.522734028</v>
+        <v>102906.8</v>
       </c>
       <c r="P113" t="n">
         <v>4700</v>
@@ -5979,10 +5979,10 @@
         <v>20</v>
       </c>
       <c r="N131" t="n">
-        <v>1367.2464516129</v>
+        <v>1324.52</v>
       </c>
       <c r="O131" t="n">
-        <v>27344.929032258</v>
+        <v>26490.4</v>
       </c>
       <c r="P131" t="n">
         <v>20500</v>
@@ -6338,10 +6338,10 @@
         <v>1</v>
       </c>
       <c r="N139" t="n">
-        <v>4937.3101733649</v>
+        <v>4937.3101737757</v>
       </c>
       <c r="O139" t="n">
-        <v>4937.3101733649</v>
+        <v>4937.3101737757</v>
       </c>
       <c r="P139" t="n">
         <v>7500</v>
@@ -6779,10 +6779,10 @@
         <v>20</v>
       </c>
       <c r="N149" t="n">
-        <v>13261.303571429</v>
+        <v>12587</v>
       </c>
       <c r="O149" t="n">
-        <v>265226.07142858</v>
+        <v>251740</v>
       </c>
       <c r="P149" t="n">
         <v>18900</v>
@@ -7129,22 +7129,22 @@
         <v>0</v>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M157" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="N157" t="n">
-        <v>2582.2548633316</v>
+        <v>2582.2548540429</v>
       </c>
       <c r="O157" t="n">
-        <v>420907.5427230508</v>
+        <v>413160.776646864</v>
       </c>
       <c r="P157" t="n">
         <v>4500</v>
       </c>
       <c r="Q157" t="n">
-        <v>733500</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="158">
@@ -7365,10 +7365,10 @@
         <v>265</v>
       </c>
       <c r="N162" t="n">
-        <v>1482.2572445348</v>
+        <v>1480</v>
       </c>
       <c r="O162" t="n">
-        <v>392798.169801722</v>
+        <v>392200</v>
       </c>
       <c r="P162" t="n">
         <v>2600</v>
@@ -7912,10 +7912,10 @@
         <v>45</v>
       </c>
       <c r="N174" t="n">
-        <v>4890.9300540176</v>
+        <v>4890.9300540541</v>
       </c>
       <c r="O174" t="n">
-        <v>220091.852430792</v>
+        <v>220091.8524324345</v>
       </c>
       <c r="P174" t="n">
         <v>8200</v>
@@ -8180,22 +8180,22 @@
         <v>0</v>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N180" t="n">
         <v>46958</v>
       </c>
       <c r="O180" t="n">
-        <v>93916</v>
+        <v>46958</v>
       </c>
       <c r="P180" t="n">
         <v>76900</v>
       </c>
       <c r="Q180" t="n">
-        <v>153800</v>
+        <v>76900</v>
       </c>
     </row>
     <row r="181">
@@ -8273,10 +8273,10 @@
         <v>54</v>
       </c>
       <c r="N182" t="n">
-        <v>7063.376059322</v>
+        <v>7041</v>
       </c>
       <c r="O182" t="n">
-        <v>381422.307203388</v>
+        <v>380214</v>
       </c>
       <c r="P182" t="n">
         <v>11500</v>
@@ -8582,22 +8582,22 @@
         <v>0</v>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M189" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N189" t="n">
-        <v>3594.2528730512</v>
+        <v>3594.2528624535</v>
       </c>
       <c r="O189" t="n">
-        <v>129393.1034298432</v>
+        <v>122204.597323419</v>
       </c>
       <c r="P189" t="n">
         <v>6500</v>
       </c>
       <c r="Q189" t="n">
-        <v>234000</v>
+        <v>221000</v>
       </c>
     </row>
     <row r="190">
@@ -8677,22 +8677,22 @@
         <v>0</v>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M191" t="n">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="N191" t="n">
         <v>489.88</v>
       </c>
       <c r="O191" t="n">
-        <v>479592.52</v>
+        <v>477143.12</v>
       </c>
       <c r="P191" t="n">
         <v>700</v>
       </c>
       <c r="Q191" t="n">
-        <v>685300</v>
+        <v>681800</v>
       </c>
     </row>
     <row r="192">
@@ -8909,10 +8909,10 @@
         <v>33</v>
       </c>
       <c r="N196" t="n">
-        <v>2093.3158067369</v>
+        <v>2090.85</v>
       </c>
       <c r="O196" t="n">
-        <v>69079.42162231769</v>
+        <v>68998.05</v>
       </c>
       <c r="P196" t="n">
         <v>2900</v>
@@ -9319,10 +9319,10 @@
         <v>174</v>
       </c>
       <c r="N205" t="n">
-        <v>3472.276319645</v>
+        <v>3472.276322317</v>
       </c>
       <c r="O205" t="n">
-        <v>604176.07961823</v>
+        <v>604176.080083158</v>
       </c>
       <c r="P205" t="n">
         <v>5900</v>
@@ -9583,22 +9583,22 @@
         <v>0</v>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M211" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N211" t="n">
-        <v>1592.5646884576</v>
+        <v>1592.5646666667</v>
       </c>
       <c r="O211" t="n">
-        <v>202255.7154341152</v>
+        <v>199070.5833333375</v>
       </c>
       <c r="P211" t="n">
         <v>3900</v>
       </c>
       <c r="Q211" t="n">
-        <v>495300</v>
+        <v>487500</v>
       </c>
     </row>
     <row r="212">
@@ -9671,10 +9671,10 @@
         <v>40</v>
       </c>
       <c r="N213" t="n">
-        <v>2231.2604819277</v>
+        <v>2224.56</v>
       </c>
       <c r="O213" t="n">
-        <v>89250.419277108</v>
+        <v>88982.39999999999</v>
       </c>
       <c r="P213" t="n">
         <v>3900</v>
@@ -10170,10 +10170,10 @@
         <v>77</v>
       </c>
       <c r="N224" t="n">
-        <v>9677.770167910399</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="O224" t="n">
-        <v>745188.3029291007</v>
+        <v>724901.87</v>
       </c>
       <c r="P224" t="n">
         <v>16900</v>
@@ -10849,22 +10849,22 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M239" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N239" t="n">
-        <v>2403.5218851304</v>
+        <v>2403.5220092133</v>
       </c>
       <c r="O239" t="n">
-        <v>12017.609425652</v>
+        <v>9614.0880368532</v>
       </c>
       <c r="P239" t="n">
         <v>3500</v>
       </c>
       <c r="Q239" t="n">
-        <v>17500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="240">
@@ -12648,10 +12648,10 @@
         <v>54</v>
       </c>
       <c r="N280" t="n">
-        <v>6207.988218663</v>
+        <v>6207.9882181666</v>
       </c>
       <c r="O280" t="n">
-        <v>335231.363807802</v>
+        <v>335231.3637809964</v>
       </c>
       <c r="P280" t="n">
         <v>9900</v>
@@ -13048,10 +13048,10 @@
         <v>45</v>
       </c>
       <c r="N289" t="n">
-        <v>4814.2679247144</v>
+        <v>4814.2679243911</v>
       </c>
       <c r="O289" t="n">
-        <v>216642.056612148</v>
+        <v>216642.0565975995</v>
       </c>
       <c r="P289" t="n">
         <v>9900</v>
@@ -13544,10 +13544,10 @@
         <v>9</v>
       </c>
       <c r="N300" t="n">
-        <v>14744.236363636</v>
+        <v>13515.55</v>
       </c>
       <c r="O300" t="n">
-        <v>132698.127272724</v>
+        <v>121639.95</v>
       </c>
       <c r="P300" t="n">
         <v>30900</v>
@@ -13984,10 +13984,10 @@
         <v>537</v>
       </c>
       <c r="N310" t="n">
-        <v>1561.0061538462</v>
+        <v>1561.0062900506</v>
       </c>
       <c r="O310" t="n">
-        <v>838260.3046154095</v>
+        <v>838260.3777571722</v>
       </c>
       <c r="P310" t="n">
         <v>2900</v>
@@ -15761,10 +15761,10 @@
         <v>5</v>
       </c>
       <c r="N349" t="n">
-        <v>18873.018181818</v>
+        <v>18536</v>
       </c>
       <c r="O349" t="n">
-        <v>94365.09090908999</v>
+        <v>92680</v>
       </c>
       <c r="P349" t="n">
         <v>30900</v>
@@ -18170,10 +18170,10 @@
         <v>51</v>
       </c>
       <c r="N401" t="n">
-        <v>10448.721014493</v>
+        <v>10411</v>
       </c>
       <c r="O401" t="n">
-        <v>532884.7717391429</v>
+        <v>530961</v>
       </c>
       <c r="P401" t="n">
         <v>16900</v>
@@ -20003,10 +20003,10 @@
         <v>144</v>
       </c>
       <c r="N441" t="n">
-        <v>2636.2357798165</v>
+        <v>2629</v>
       </c>
       <c r="O441" t="n">
-        <v>379617.952293576</v>
+        <v>378576</v>
       </c>
       <c r="P441" t="n">
         <v>4500</v>
@@ -20233,10 +20233,10 @@
         <v>95</v>
       </c>
       <c r="N446" t="n">
-        <v>6650.5777839955</v>
+        <v>6645</v>
       </c>
       <c r="O446" t="n">
-        <v>631804.8894795725</v>
+        <v>631275</v>
       </c>
       <c r="P446" t="n">
         <v>10900</v>
@@ -21378,10 +21378,10 @@
         <v>7</v>
       </c>
       <c r="N471" t="n">
-        <v>18170.288401254</v>
+        <v>18001</v>
       </c>
       <c r="O471" t="n">
-        <v>127192.018808778</v>
+        <v>126007</v>
       </c>
       <c r="P471" t="n">
         <v>28900</v>
@@ -22209,10 +22209,10 @@
         <v>5</v>
       </c>
       <c r="N489" t="n">
-        <v>10795.831156812</v>
+        <v>10713.21</v>
       </c>
       <c r="O489" t="n">
-        <v>53979.15578406</v>
+        <v>53566.05</v>
       </c>
       <c r="P489" t="n">
         <v>20900</v>
@@ -22856,10 +22856,10 @@
         <v>294</v>
       </c>
       <c r="N503" t="n">
-        <v>1516.0387131507</v>
+        <v>1516.0387126124</v>
       </c>
       <c r="O503" t="n">
-        <v>445715.3816663058</v>
+        <v>445715.3815080457</v>
       </c>
       <c r="P503" t="n">
         <v>2300</v>
@@ -24204,10 +24204,10 @@
         <v>1</v>
       </c>
       <c r="N532" t="n">
-        <v>5510.92</v>
+        <v>6178.9103030303</v>
       </c>
       <c r="O532" t="n">
-        <v>5510.92</v>
+        <v>6178.9103030303</v>
       </c>
       <c r="P532" t="n">
         <v>4900</v>
@@ -25695,10 +25695,10 @@
         <v>363</v>
       </c>
       <c r="N564" t="n">
-        <v>1333.9879518072</v>
+        <v>1326</v>
       </c>
       <c r="O564" t="n">
-        <v>484237.6265060136</v>
+        <v>481338</v>
       </c>
       <c r="P564" t="n">
         <v>2900</v>
@@ -25872,22 +25872,22 @@
         <v>0</v>
       </c>
       <c r="L568" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M568" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="N568" t="n">
-        <v>517.29622957051</v>
+        <v>517.29632575033</v>
       </c>
       <c r="O568" t="n">
-        <v>12932.40573926275</v>
+        <v>4138.37060600264</v>
       </c>
       <c r="P568" t="n">
         <v>900</v>
       </c>
       <c r="Q568" t="n">
-        <v>22500</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="569">
@@ -26063,10 +26063,10 @@
         <v>1236</v>
       </c>
       <c r="N572" t="n">
-        <v>703.79465893216</v>
+        <v>703.79465786602</v>
       </c>
       <c r="O572" t="n">
-        <v>869890.1984401498</v>
+        <v>869890.1971224007</v>
       </c>
       <c r="P572" t="n">
         <v>900</v>
@@ -26250,22 +26250,22 @@
         <v>0</v>
       </c>
       <c r="L576" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M576" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N576" t="n">
-        <v>1595.4982940252</v>
+        <v>1595.4982440945</v>
       </c>
       <c r="O576" t="n">
-        <v>119662.37205189</v>
+        <v>116471.3718188985</v>
       </c>
       <c r="P576" t="n">
         <v>2500</v>
       </c>
       <c r="Q576" t="n">
-        <v>187500</v>
+        <v>182500</v>
       </c>
     </row>
     <row r="577">
@@ -28808,10 +28808,10 @@
         <v>18</v>
       </c>
       <c r="N629" t="n">
-        <v>3099.0394791667</v>
+        <v>3067.090625</v>
       </c>
       <c r="O629" t="n">
-        <v>55782.7106250006</v>
+        <v>55207.63125</v>
       </c>
       <c r="P629" t="n">
         <v>7200</v>
@@ -33208,22 +33208,22 @@
         <v>0</v>
       </c>
       <c r="L723" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M723" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="N723" t="n">
         <v>1584</v>
       </c>
       <c r="O723" t="n">
-        <v>567072</v>
+        <v>562320</v>
       </c>
       <c r="P723" t="n">
         <v>2000</v>
       </c>
       <c r="Q723" t="n">
-        <v>716000</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="724">
@@ -36138,22 +36138,22 @@
         <v>0</v>
       </c>
       <c r="L786" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M786" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="N786" t="n">
         <v>2465</v>
       </c>
       <c r="O786" t="n">
-        <v>872610</v>
+        <v>867680</v>
       </c>
       <c r="P786" t="n">
         <v>3000</v>
       </c>
       <c r="Q786" t="n">
-        <v>1062000</v>
+        <v>1056000</v>
       </c>
     </row>
     <row r="787">
@@ -36187,22 +36187,22 @@
         <v>0</v>
       </c>
       <c r="L787" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M787" t="n">
-        <v>2627</v>
+        <v>2615</v>
       </c>
       <c r="N787" t="n">
         <v>467</v>
       </c>
       <c r="O787" t="n">
-        <v>1226809</v>
+        <v>1221205</v>
       </c>
       <c r="P787" t="n">
         <v>600</v>
       </c>
       <c r="Q787" t="n">
-        <v>1576200</v>
+        <v>1569000</v>
       </c>
     </row>
     <row r="788">
@@ -36236,22 +36236,22 @@
         <v>0</v>
       </c>
       <c r="L788" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M788" t="n">
-        <v>2503</v>
+        <v>2491</v>
       </c>
       <c r="N788" t="n">
         <v>425</v>
       </c>
       <c r="O788" t="n">
-        <v>1063775</v>
+        <v>1058675</v>
       </c>
       <c r="P788" t="n">
         <v>500</v>
       </c>
       <c r="Q788" t="n">
-        <v>1251500</v>
+        <v>1245500</v>
       </c>
     </row>
     <row r="789">
@@ -36285,22 +36285,22 @@
         <v>0</v>
       </c>
       <c r="L789" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M789" t="n">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="N789" t="n">
         <v>1700</v>
       </c>
       <c r="O789" t="n">
-        <v>630700</v>
+        <v>625600</v>
       </c>
       <c r="P789" t="n">
         <v>2000</v>
       </c>
       <c r="Q789" t="n">
-        <v>742000</v>
+        <v>736000</v>
       </c>
     </row>
     <row r="790">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -7451,22 +7451,22 @@
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M164" t="n">
-        <v>835</v>
+        <v>825</v>
       </c>
       <c r="N164" t="n">
         <v>156.25</v>
       </c>
       <c r="O164" t="n">
-        <v>130468.75</v>
+        <v>128906.25</v>
       </c>
       <c r="P164" t="n">
         <v>250</v>
       </c>
       <c r="Q164" t="n">
-        <v>208750</v>
+        <v>206250</v>
       </c>
     </row>
     <row r="165">
@@ -8677,22 +8677,22 @@
         <v>0</v>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M191" t="n">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="N191" t="n">
         <v>489.88</v>
       </c>
       <c r="O191" t="n">
-        <v>477143.12</v>
+        <v>474203.84</v>
       </c>
       <c r="P191" t="n">
         <v>700</v>
       </c>
       <c r="Q191" t="n">
-        <v>681800</v>
+        <v>677600</v>
       </c>
     </row>
     <row r="192">
@@ -21427,10 +21427,10 @@
         <v>23</v>
       </c>
       <c r="N472" t="n">
-        <v>10755</v>
+        <v>10795.738636364</v>
       </c>
       <c r="O472" t="n">
-        <v>247365</v>
+        <v>248301.988636372</v>
       </c>
       <c r="P472" t="n">
         <v>17900</v>
@@ -26017,10 +26017,10 @@
         <v>1146</v>
       </c>
       <c r="N571" t="n">
-        <v>703.79463731331</v>
+        <v>703.79463559345</v>
       </c>
       <c r="O571" t="n">
-        <v>806548.6543610533</v>
+        <v>806548.6523900938</v>
       </c>
       <c r="P571" t="n">
         <v>900</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-27</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-28</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -556,10 +556,10 @@
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27065.693430657</v>
       </c>
       <c r="O4" t="n">
-        <v>54000</v>
+        <v>54131.386861314</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -865,10 +865,10 @@
         <v>9</v>
       </c>
       <c r="N11" t="n">
-        <v>27000</v>
+        <v>27109.756097561</v>
       </c>
       <c r="O11" t="n">
-        <v>243000</v>
+        <v>243987.804878049</v>
       </c>
       <c r="P11" t="n">
         <v>20000</v>
@@ -1423,22 +1423,22 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N25" t="n">
-        <v>27000</v>
+        <v>27267.326732673</v>
       </c>
       <c r="O25" t="n">
-        <v>486000</v>
+        <v>409009.900990095</v>
       </c>
       <c r="P25" t="n">
         <v>20000</v>
       </c>
       <c r="Q25" t="n">
-        <v>360000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="26">
@@ -1462,22 +1462,22 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>27000</v>
+        <v>27151.898734177</v>
       </c>
       <c r="O26" t="n">
-        <v>162000</v>
+        <v>81455.69620253101</v>
       </c>
       <c r="P26" t="n">
         <v>20000</v>
       </c>
       <c r="Q26" t="n">
-        <v>120000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="27">
@@ -1663,10 +1663,10 @@
         <v>15</v>
       </c>
       <c r="N31" t="n">
-        <v>3926.8370711297</v>
+        <v>3926.837066527</v>
       </c>
       <c r="O31" t="n">
-        <v>58902.55606694549</v>
+        <v>58902.555997905</v>
       </c>
       <c r="P31" t="n">
         <v>4800</v>
@@ -1864,10 +1864,10 @@
         <v>57</v>
       </c>
       <c r="N36" t="n">
-        <v>3716.3301970443</v>
+        <v>3716.3301973684</v>
       </c>
       <c r="O36" t="n">
-        <v>211830.8212315251</v>
+        <v>211830.8212499988</v>
       </c>
       <c r="P36" t="n">
         <v>9500</v>
@@ -3994,22 +3994,22 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M85" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N85" t="n">
-        <v>27000</v>
+        <v>27352.173913043</v>
       </c>
       <c r="O85" t="n">
-        <v>270000</v>
+        <v>191465.217391301</v>
       </c>
       <c r="P85" t="n">
         <v>20000</v>
       </c>
       <c r="Q85" t="n">
-        <v>200000</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="86">
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -4075,19 +4075,19 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N87" t="n">
         <v>1141.57</v>
       </c>
       <c r="O87" t="n">
-        <v>63927.92</v>
+        <v>62786.35</v>
       </c>
       <c r="P87" t="n">
         <v>3900</v>
       </c>
       <c r="Q87" t="n">
-        <v>218400</v>
+        <v>214500</v>
       </c>
     </row>
     <row r="88">
@@ -6245,22 +6245,22 @@
         <v>0</v>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M137" t="n">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="N137" t="n">
         <v>2833</v>
       </c>
       <c r="O137" t="n">
-        <v>1932106</v>
+        <v>1915108</v>
       </c>
       <c r="P137" t="n">
         <v>3500</v>
       </c>
       <c r="Q137" t="n">
-        <v>2387000</v>
+        <v>2366000</v>
       </c>
     </row>
     <row r="138">
@@ -7042,22 +7042,22 @@
         <v>0</v>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M155" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N155" t="n">
         <v>2804.33</v>
       </c>
       <c r="O155" t="n">
-        <v>213129.08</v>
+        <v>204716.09</v>
       </c>
       <c r="P155" t="n">
         <v>4900</v>
       </c>
       <c r="Q155" t="n">
-        <v>372400</v>
+        <v>357700</v>
       </c>
     </row>
     <row r="156">
@@ -7083,22 +7083,22 @@
         <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M156" t="n">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="N156" t="n">
         <v>1194.83</v>
       </c>
       <c r="O156" t="n">
-        <v>408631.86</v>
+        <v>394293.9</v>
       </c>
       <c r="P156" t="n">
         <v>2500</v>
       </c>
       <c r="Q156" t="n">
-        <v>855000</v>
+        <v>825000</v>
       </c>
     </row>
     <row r="157">
@@ -7135,10 +7135,10 @@
         <v>153</v>
       </c>
       <c r="N157" t="n">
-        <v>2582.2548125</v>
+        <v>2582.2547989556</v>
       </c>
       <c r="O157" t="n">
-        <v>395084.9863125</v>
+        <v>395084.9842402068</v>
       </c>
       <c r="P157" t="n">
         <v>4500</v>
@@ -7175,22 +7175,22 @@
         <v>0</v>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M158" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="N158" t="n">
-        <v>10600</v>
+        <v>10614.851138354</v>
       </c>
       <c r="O158" t="n">
-        <v>1081200</v>
+        <v>976566.3047285681</v>
       </c>
       <c r="P158" t="n">
         <v>17200</v>
       </c>
       <c r="Q158" t="n">
-        <v>1754400</v>
+        <v>1582400</v>
       </c>
     </row>
     <row r="159">
@@ -7218,25 +7218,25 @@
         <v>133</v>
       </c>
       <c r="K159" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="N159" t="n">
         <v>5216.895823058</v>
       </c>
       <c r="O159" t="n">
-        <v>693847.144466714</v>
+        <v>798185.0609278741</v>
       </c>
       <c r="P159" t="n">
         <v>8500</v>
       </c>
       <c r="Q159" t="n">
-        <v>1130500</v>
+        <v>1300500</v>
       </c>
     </row>
     <row r="160">
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
@@ -7454,19 +7454,19 @@
         <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="N164" t="n">
         <v>156.25</v>
       </c>
       <c r="O164" t="n">
-        <v>108593.75</v>
+        <v>107031.25</v>
       </c>
       <c r="P164" t="n">
         <v>250</v>
       </c>
       <c r="Q164" t="n">
-        <v>173750</v>
+        <v>171250</v>
       </c>
     </row>
     <row r="165">
@@ -7912,10 +7912,10 @@
         <v>68</v>
       </c>
       <c r="N174" t="n">
-        <v>4890.9300552868</v>
+        <v>4890.930055517</v>
       </c>
       <c r="O174" t="n">
-        <v>332583.2437595024</v>
+        <v>332583.243775156</v>
       </c>
       <c r="P174" t="n">
         <v>8200</v>
@@ -8677,22 +8677,22 @@
         <v>0</v>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M191" t="n">
-        <v>944</v>
+        <v>896</v>
       </c>
       <c r="N191" t="n">
         <v>489.88</v>
       </c>
       <c r="O191" t="n">
-        <v>462446.72</v>
+        <v>438932.48</v>
       </c>
       <c r="P191" t="n">
         <v>700</v>
       </c>
       <c r="Q191" t="n">
-        <v>660800</v>
+        <v>627200</v>
       </c>
     </row>
     <row r="192">
@@ -8821,10 +8821,10 @@
         <v>51</v>
       </c>
       <c r="N194" t="n">
-        <v>14822.378817006</v>
+        <v>14822.378814083</v>
       </c>
       <c r="O194" t="n">
-        <v>755941.319667306</v>
+        <v>755941.319518233</v>
       </c>
       <c r="P194" t="n">
         <v>24900</v>
@@ -9142,10 +9142,10 @@
         <v>48</v>
       </c>
       <c r="N201" t="n">
-        <v>12422.463007951</v>
+        <v>12422.463013274</v>
       </c>
       <c r="O201" t="n">
-        <v>596278.224381648</v>
+        <v>596278.224637152</v>
       </c>
       <c r="P201" t="n">
         <v>19900</v>
@@ -9319,10 +9319,10 @@
         <v>162</v>
       </c>
       <c r="N205" t="n">
-        <v>3472.2763500602</v>
+        <v>3472.2763717066</v>
       </c>
       <c r="O205" t="n">
-        <v>562508.7687097524</v>
+        <v>562508.7722164692</v>
       </c>
       <c r="P205" t="n">
         <v>5900</v>
@@ -9497,10 +9497,10 @@
         <v>116</v>
       </c>
       <c r="N209" t="n">
-        <v>3041.6600149925</v>
+        <v>3041.660015015</v>
       </c>
       <c r="O209" t="n">
-        <v>352832.5617391299</v>
+        <v>352832.56174174</v>
       </c>
       <c r="P209" t="n">
         <v>5500</v>
@@ -9543,10 +9543,10 @@
         <v>58</v>
       </c>
       <c r="N210" t="n">
-        <v>4371.1729689003</v>
+        <v>4371.1729703288</v>
       </c>
       <c r="O210" t="n">
-        <v>253528.0321962174</v>
+        <v>253528.0322790704</v>
       </c>
       <c r="P210" t="n">
         <v>8900</v>
@@ -9583,22 +9583,22 @@
         <v>0</v>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M211" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="N211" t="n">
-        <v>1592.5645263158</v>
+        <v>1592.5644086022</v>
       </c>
       <c r="O211" t="n">
-        <v>192700.3076842118</v>
+        <v>173589.5205376398</v>
       </c>
       <c r="P211" t="n">
         <v>3900</v>
       </c>
       <c r="Q211" t="n">
-        <v>471900</v>
+        <v>425100</v>
       </c>
     </row>
     <row r="212">
@@ -9893,22 +9893,22 @@
         <v>0</v>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M218" t="n">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="N218" t="n">
         <v>4648.6</v>
       </c>
       <c r="O218" t="n">
-        <v>1259770.6</v>
+        <v>1250473.4</v>
       </c>
       <c r="P218" t="n">
         <v>8900</v>
       </c>
       <c r="Q218" t="n">
-        <v>2411900</v>
+        <v>2394100</v>
       </c>
     </row>
     <row r="219">
@@ -9942,22 +9942,22 @@
         <v>0</v>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M219" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="N219" t="n">
         <v>1770.37</v>
       </c>
       <c r="O219" t="n">
-        <v>270866.61</v>
+        <v>267325.87</v>
       </c>
       <c r="P219" t="n">
         <v>3900</v>
       </c>
       <c r="Q219" t="n">
-        <v>596700</v>
+        <v>588900</v>
       </c>
     </row>
     <row r="220">
@@ -10032,22 +10032,22 @@
         <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M221" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N221" t="n">
         <v>17472.91</v>
       </c>
       <c r="O221" t="n">
-        <v>926064.23</v>
+        <v>716389.3099999999</v>
       </c>
       <c r="P221" t="n">
         <v>2900</v>
       </c>
       <c r="Q221" t="n">
-        <v>153700</v>
+        <v>118900</v>
       </c>
     </row>
     <row r="222">
@@ -10358,10 +10358,10 @@
         <v>170</v>
       </c>
       <c r="N228" t="n">
-        <v>4635.49</v>
+        <v>4768.3543630573</v>
       </c>
       <c r="O228" t="n">
-        <v>788033.2999999999</v>
+        <v>810620.241719741</v>
       </c>
       <c r="P228" t="n">
         <v>7500</v>
@@ -10669,22 +10669,22 @@
         <v>0</v>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M235" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N235" t="n">
         <v>11921.4</v>
       </c>
       <c r="O235" t="n">
-        <v>655677</v>
+        <v>631834.2</v>
       </c>
       <c r="P235" t="n">
         <v>19900</v>
       </c>
       <c r="Q235" t="n">
-        <v>1094500</v>
+        <v>1054700</v>
       </c>
     </row>
     <row r="236">
@@ -10754,22 +10754,22 @@
         <v>0</v>
       </c>
       <c r="L237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M237" t="n">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="N237" t="n">
         <v>3751</v>
       </c>
       <c r="O237" t="n">
-        <v>2528174</v>
+        <v>2520672</v>
       </c>
       <c r="P237" t="n">
         <v>6400</v>
       </c>
       <c r="Q237" t="n">
-        <v>4313600</v>
+        <v>4300800</v>
       </c>
     </row>
     <row r="238">
@@ -11028,22 +11028,22 @@
         <v>0</v>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M243" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="N243" t="n">
         <v>2638</v>
       </c>
       <c r="O243" t="n">
-        <v>379872</v>
+        <v>364044</v>
       </c>
       <c r="P243" t="n">
         <v>4500</v>
       </c>
       <c r="Q243" t="n">
-        <v>648000</v>
+        <v>621000</v>
       </c>
     </row>
     <row r="244">
@@ -11820,22 +11820,22 @@
         <v>0</v>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M261" t="n">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="N261" t="n">
         <v>2567</v>
       </c>
       <c r="O261" t="n">
-        <v>1496561</v>
+        <v>1465757</v>
       </c>
       <c r="P261" t="n">
         <v>4500</v>
       </c>
       <c r="Q261" t="n">
-        <v>2623500</v>
+        <v>2569500</v>
       </c>
     </row>
     <row r="262">
@@ -11902,22 +11902,22 @@
         <v>0</v>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M263" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N263" t="n">
         <v>2517.22</v>
       </c>
       <c r="O263" t="n">
-        <v>229067.02</v>
+        <v>213963.7</v>
       </c>
       <c r="P263" t="n">
         <v>4200</v>
       </c>
       <c r="Q263" t="n">
-        <v>382200</v>
+        <v>357000</v>
       </c>
     </row>
     <row r="264">
@@ -11943,22 +11943,22 @@
         <v>0</v>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M264" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="N264" t="n">
-        <v>2029.8742253521</v>
+        <v>2029.8742541123</v>
       </c>
       <c r="O264" t="n">
-        <v>286212.2657746461</v>
+        <v>261853.7787804867</v>
       </c>
       <c r="P264" t="n">
         <v>3600</v>
       </c>
       <c r="Q264" t="n">
-        <v>507600</v>
+        <v>464400</v>
       </c>
     </row>
     <row r="265">
@@ -12238,22 +12238,22 @@
         <v>0</v>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M271" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N271" t="n">
-        <v>2680.7396931747</v>
+        <v>2680.7396929825</v>
       </c>
       <c r="O271" t="n">
-        <v>166205.8609768314</v>
+        <v>163525.1212719325</v>
       </c>
       <c r="P271" t="n">
         <v>4900</v>
       </c>
       <c r="Q271" t="n">
-        <v>303800</v>
+        <v>298900</v>
       </c>
     </row>
     <row r="272">
@@ -12423,10 +12423,10 @@
         <v>53</v>
       </c>
       <c r="N275" t="n">
-        <v>30611</v>
+        <v>30745.062773723</v>
       </c>
       <c r="O275" t="n">
-        <v>1622383</v>
+        <v>1629488.327007319</v>
       </c>
       <c r="P275" t="n">
         <v>38900</v>
@@ -12504,22 +12504,22 @@
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="M277" t="n">
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="N277" t="n">
-        <v>1651</v>
+        <v>3271.8447488584</v>
       </c>
       <c r="O277" t="n">
-        <v>709930</v>
+        <v>0</v>
       </c>
       <c r="P277" t="n">
         <v>2500</v>
       </c>
       <c r="Q277" t="n">
-        <v>1075000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -12593,25 +12593,25 @@
         <v>23</v>
       </c>
       <c r="K279" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L279" t="n">
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="N279" t="n">
-        <v>6207.9882021366</v>
+        <v>6207.9882013781</v>
       </c>
       <c r="O279" t="n">
-        <v>142783.7286491418</v>
+        <v>453183.1387006013</v>
       </c>
       <c r="P279" t="n">
         <v>9900</v>
       </c>
       <c r="Q279" t="n">
-        <v>227700</v>
+        <v>722700</v>
       </c>
     </row>
     <row r="280">
@@ -12697,10 +12697,10 @@
         <v>74</v>
       </c>
       <c r="N281" t="n">
-        <v>4285.1965633075</v>
+        <v>4285.1966145833</v>
       </c>
       <c r="O281" t="n">
-        <v>317104.545684755</v>
+        <v>317104.5494791642</v>
       </c>
       <c r="P281" t="n">
         <v>6900</v>
@@ -12863,22 +12863,22 @@
         <v>0</v>
       </c>
       <c r="L285" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M285" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="N285" t="n">
-        <v>1106</v>
+        <v>1111.1642023346</v>
       </c>
       <c r="O285" t="n">
-        <v>92904</v>
+        <v>86670.80778209881</v>
       </c>
       <c r="P285" t="n">
         <v>2100</v>
       </c>
       <c r="Q285" t="n">
-        <v>176400</v>
+        <v>163800</v>
       </c>
     </row>
     <row r="286">
@@ -12904,22 +12904,22 @@
         <v>0</v>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M286" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="N286" t="n">
-        <v>1430.38</v>
+        <v>1447.7706382979</v>
       </c>
       <c r="O286" t="n">
-        <v>221708.9</v>
+        <v>218613.3663829829</v>
       </c>
       <c r="P286" t="n">
         <v>4000</v>
       </c>
       <c r="Q286" t="n">
-        <v>620000</v>
+        <v>604000</v>
       </c>
     </row>
     <row r="287">
@@ -13002,10 +13002,10 @@
         <v>70</v>
       </c>
       <c r="N288" t="n">
-        <v>4814.2633769677</v>
+        <v>4814.2633736737</v>
       </c>
       <c r="O288" t="n">
-        <v>336998.436387739</v>
+        <v>336998.436157159</v>
       </c>
       <c r="P288" t="n">
         <v>9900</v>
@@ -13089,10 +13089,10 @@
         <v>19</v>
       </c>
       <c r="N290" t="n">
-        <v>11562.038395415</v>
+        <v>11562.038381503</v>
       </c>
       <c r="O290" t="n">
-        <v>219678.729512885</v>
+        <v>219678.729248557</v>
       </c>
       <c r="P290" t="n">
         <v>18500</v>
@@ -13135,10 +13135,10 @@
         <v>36</v>
       </c>
       <c r="N291" t="n">
-        <v>13513.643534483</v>
+        <v>13513.643727273</v>
       </c>
       <c r="O291" t="n">
-        <v>486491.167241388</v>
+        <v>486491.174181828</v>
       </c>
       <c r="P291" t="n">
         <v>21900</v>
@@ -13590,10 +13590,10 @@
         <v>7</v>
       </c>
       <c r="N301" t="n">
-        <v>27123.764688797</v>
+        <v>27123.764610526</v>
       </c>
       <c r="O301" t="n">
-        <v>189866.352821579</v>
+        <v>189866.352273682</v>
       </c>
       <c r="P301" t="n">
         <v>44500</v>
@@ -13805,10 +13805,10 @@
         <v>13</v>
       </c>
       <c r="N306" t="n">
-        <v>8332.7796042216</v>
+        <v>8332.7795967742</v>
       </c>
       <c r="O306" t="n">
-        <v>108326.1348548808</v>
+        <v>108326.1347580646</v>
       </c>
       <c r="P306" t="n">
         <v>14900</v>
@@ -13932,22 +13932,22 @@
         <v>0</v>
       </c>
       <c r="L309" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M309" t="n">
-        <v>532</v>
+        <v>500</v>
       </c>
       <c r="N309" t="n">
-        <v>1561.0066122098</v>
+        <v>1561.0072654155</v>
       </c>
       <c r="O309" t="n">
-        <v>830455.5176956137</v>
+        <v>780503.63270775</v>
       </c>
       <c r="P309" t="n">
         <v>2900</v>
       </c>
       <c r="Q309" t="n">
-        <v>1542800</v>
+        <v>1450000</v>
       </c>
     </row>
     <row r="310">
@@ -14030,10 +14030,10 @@
         <v>31</v>
       </c>
       <c r="N311" t="n">
-        <v>26854</v>
+        <v>27080.935211268</v>
       </c>
       <c r="O311" t="n">
-        <v>832474</v>
+        <v>839508.9915493079</v>
       </c>
       <c r="P311" t="n">
         <v>43900</v>
@@ -14370,22 +14370,22 @@
         <v>0</v>
       </c>
       <c r="L319" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M319" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N319" t="n">
         <v>9627.34</v>
       </c>
       <c r="O319" t="n">
-        <v>423602.96</v>
+        <v>404348.28</v>
       </c>
       <c r="P319" t="n">
         <v>15900</v>
       </c>
       <c r="Q319" t="n">
-        <v>699600</v>
+        <v>667800</v>
       </c>
     </row>
     <row r="320">
@@ -14884,10 +14884,10 @@
         <v>228</v>
       </c>
       <c r="N330" t="n">
-        <v>7700</v>
+        <v>7738.024691358</v>
       </c>
       <c r="O330" t="n">
-        <v>1755600</v>
+        <v>1764269.629629624</v>
       </c>
       <c r="P330" t="n">
         <v>13900</v>
@@ -15430,22 +15430,22 @@
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M342" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N342" t="n">
         <v>5194</v>
       </c>
       <c r="O342" t="n">
-        <v>363580</v>
+        <v>347998</v>
       </c>
       <c r="P342" t="n">
         <v>9000</v>
       </c>
       <c r="Q342" t="n">
-        <v>630000</v>
+        <v>603000</v>
       </c>
     </row>
     <row r="343">
@@ -15709,22 +15709,22 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M348" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N348" t="n">
         <v>18536</v>
       </c>
       <c r="O348" t="n">
-        <v>92680</v>
+        <v>74144</v>
       </c>
       <c r="P348" t="n">
         <v>30900</v>
       </c>
       <c r="Q348" t="n">
-        <v>154500</v>
+        <v>123600</v>
       </c>
     </row>
     <row r="349">
@@ -15801,22 +15801,22 @@
         <v>0</v>
       </c>
       <c r="L350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M350" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N350" t="n">
         <v>15824</v>
       </c>
       <c r="O350" t="n">
-        <v>458896</v>
+        <v>443072</v>
       </c>
       <c r="P350" t="n">
         <v>26900</v>
       </c>
       <c r="Q350" t="n">
-        <v>780100</v>
+        <v>753200</v>
       </c>
     </row>
     <row r="351">
@@ -15991,10 +15991,10 @@
         <v>12</v>
       </c>
       <c r="N354" t="n">
-        <v>23521.622708333</v>
+        <v>23521.621666667</v>
       </c>
       <c r="O354" t="n">
-        <v>282259.472499996</v>
+        <v>282259.460000004</v>
       </c>
       <c r="P354" t="n">
         <v>39000</v>
@@ -16037,10 +16037,10 @@
         <v>39</v>
       </c>
       <c r="N355" t="n">
-        <v>1778.4728840436</v>
+        <v>1778.4728878597</v>
       </c>
       <c r="O355" t="n">
-        <v>69360.4424777004</v>
+        <v>69360.4426265283</v>
       </c>
       <c r="P355" t="n">
         <v>4900</v>
@@ -16083,10 +16083,10 @@
         <v>65</v>
       </c>
       <c r="N356" t="n">
-        <v>22739</v>
+        <v>22935.194995686</v>
       </c>
       <c r="O356" t="n">
-        <v>1478035</v>
+        <v>1490787.67471959</v>
       </c>
       <c r="P356" t="n">
         <v>36900</v>
@@ -16175,10 +16175,10 @@
         <v>58</v>
       </c>
       <c r="N358" t="n">
-        <v>16058</v>
+        <v>16177.301634473</v>
       </c>
       <c r="O358" t="n">
-        <v>931364</v>
+        <v>938283.494799434</v>
       </c>
       <c r="P358" t="n">
         <v>25900</v>
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="J373" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K373" t="n">
         <v>0</v>
@@ -16865,19 +16865,19 @@
         <v>0</v>
       </c>
       <c r="M373" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N373" t="n">
-        <v>3259.2102666667</v>
+        <v>3259.2102702703</v>
       </c>
       <c r="O373" t="n">
-        <v>104294.7285333344</v>
+        <v>101035.5183783793</v>
       </c>
       <c r="P373" t="n">
         <v>5300</v>
       </c>
       <c r="Q373" t="n">
-        <v>169600</v>
+        <v>164300</v>
       </c>
     </row>
     <row r="374">
@@ -17753,10 +17753,10 @@
         <v>14</v>
       </c>
       <c r="N392" t="n">
-        <v>11857</v>
+        <v>12344.273972603</v>
       </c>
       <c r="O392" t="n">
-        <v>165998</v>
+        <v>172819.835616442</v>
       </c>
       <c r="P392" t="n">
         <v>19900</v>
@@ -17937,10 +17937,10 @@
         <v>8</v>
       </c>
       <c r="N396" t="n">
-        <v>28116</v>
+        <v>28661.941747573</v>
       </c>
       <c r="O396" t="n">
-        <v>224928</v>
+        <v>229295.533980584</v>
       </c>
       <c r="P396" t="n">
         <v>45900</v>
@@ -18072,22 +18072,22 @@
         <v>0</v>
       </c>
       <c r="L399" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M399" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N399" t="n">
         <v>8858.16</v>
       </c>
       <c r="O399" t="n">
-        <v>336610.08</v>
+        <v>318893.76</v>
       </c>
       <c r="P399" t="n">
         <v>15500</v>
       </c>
       <c r="Q399" t="n">
-        <v>589000</v>
+        <v>558000</v>
       </c>
     </row>
     <row r="400">
@@ -18302,22 +18302,22 @@
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M404" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="N404" t="n">
-        <v>2252.3008997955</v>
+        <v>2252.3011740042</v>
       </c>
       <c r="O404" t="n">
-        <v>45046.01799591</v>
+        <v>18018.4093920336</v>
       </c>
       <c r="P404" t="n">
         <v>3900</v>
       </c>
       <c r="Q404" t="n">
-        <v>78000</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="405">
@@ -18725,10 +18725,10 @@
         <v>67</v>
       </c>
       <c r="N413" t="n">
-        <v>3519</v>
+        <v>4129.9375</v>
       </c>
       <c r="O413" t="n">
-        <v>235773</v>
+        <v>276705.8125</v>
       </c>
       <c r="P413" t="n">
         <v>5900</v>
@@ -18949,22 +18949,22 @@
         <v>0</v>
       </c>
       <c r="L418" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M418" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N418" t="n">
         <v>3396.38</v>
       </c>
       <c r="O418" t="n">
-        <v>220764.7</v>
+        <v>207179.18</v>
       </c>
       <c r="P418" t="n">
         <v>6500</v>
       </c>
       <c r="Q418" t="n">
-        <v>422500</v>
+        <v>396500</v>
       </c>
     </row>
     <row r="419">
@@ -19047,10 +19047,10 @@
         <v>133</v>
       </c>
       <c r="N420" t="n">
-        <v>4907.8227973568</v>
+        <v>4907.8228159645</v>
       </c>
       <c r="O420" t="n">
-        <v>652740.4320484544</v>
+        <v>652740.4345232785</v>
       </c>
       <c r="P420" t="n">
         <v>8200</v>
@@ -19410,10 +19410,10 @@
         <v>17</v>
       </c>
       <c r="N428" t="n">
-        <v>20726</v>
+        <v>21286.162162162</v>
       </c>
       <c r="O428" t="n">
-        <v>352342</v>
+        <v>361864.756756754</v>
       </c>
       <c r="P428" t="n">
         <v>33900</v>
@@ -19497,10 +19497,10 @@
         <v>35</v>
       </c>
       <c r="N430" t="n">
-        <v>20731</v>
+        <v>21767.55</v>
       </c>
       <c r="O430" t="n">
-        <v>725585</v>
+        <v>761864.25</v>
       </c>
       <c r="P430" t="n">
         <v>33900</v>
@@ -19997,22 +19997,22 @@
         <v>0</v>
       </c>
       <c r="L441" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M441" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="N441" t="n">
         <v>6849.2</v>
       </c>
       <c r="O441" t="n">
-        <v>1267102</v>
+        <v>1246554.4</v>
       </c>
       <c r="P441" t="n">
         <v>11500</v>
       </c>
       <c r="Q441" t="n">
-        <v>2127500</v>
+        <v>2093000</v>
       </c>
     </row>
     <row r="442">
@@ -20089,22 +20089,22 @@
         <v>0</v>
       </c>
       <c r="L443" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M443" t="n">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="N443" t="n">
         <v>5772</v>
       </c>
       <c r="O443" t="n">
-        <v>1102452</v>
+        <v>1050504</v>
       </c>
       <c r="P443" t="n">
         <v>9900</v>
       </c>
       <c r="Q443" t="n">
-        <v>1890900</v>
+        <v>1801800</v>
       </c>
     </row>
     <row r="444">
@@ -20417,10 +20417,10 @@
         <v>19</v>
       </c>
       <c r="N450" t="n">
-        <v>13565</v>
+        <v>13585.998452012</v>
       </c>
       <c r="O450" t="n">
-        <v>257735</v>
+        <v>258133.970588228</v>
       </c>
       <c r="P450" t="n">
         <v>22500</v>
@@ -20503,22 +20503,22 @@
         <v>0</v>
       </c>
       <c r="L452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M452" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N452" t="n">
         <v>24480</v>
       </c>
       <c r="O452" t="n">
-        <v>1150560</v>
+        <v>1126080</v>
       </c>
       <c r="P452" t="n">
         <v>39900</v>
       </c>
       <c r="Q452" t="n">
-        <v>1875300</v>
+        <v>1835400</v>
       </c>
     </row>
     <row r="453">
@@ -20647,10 +20647,10 @@
         <v>29</v>
       </c>
       <c r="N455" t="n">
-        <v>23439</v>
+        <v>24040</v>
       </c>
       <c r="O455" t="n">
-        <v>679731</v>
+        <v>697160</v>
       </c>
       <c r="P455" t="n">
         <v>37900</v>
@@ -20693,10 +20693,10 @@
         <v>46</v>
       </c>
       <c r="N456" t="n">
-        <v>19008</v>
+        <v>19059.165545087</v>
       </c>
       <c r="O456" t="n">
-        <v>874368</v>
+        <v>876721.615074002</v>
       </c>
       <c r="P456" t="n">
         <v>30900</v>
@@ -20785,10 +20785,10 @@
         <v>51</v>
       </c>
       <c r="N458" t="n">
-        <v>17992</v>
+        <v>18038.854166667</v>
       </c>
       <c r="O458" t="n">
-        <v>917592</v>
+        <v>919981.562500017</v>
       </c>
       <c r="P458" t="n">
         <v>28900</v>
@@ -20917,22 +20917,22 @@
         <v>0</v>
       </c>
       <c r="L461" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M461" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="N461" t="n">
         <v>11348</v>
       </c>
       <c r="O461" t="n">
-        <v>567400</v>
+        <v>522008</v>
       </c>
       <c r="P461" t="n">
         <v>19900</v>
       </c>
       <c r="Q461" t="n">
-        <v>995000</v>
+        <v>915400</v>
       </c>
     </row>
     <row r="462">
@@ -20969,10 +20969,10 @@
         <v>143</v>
       </c>
       <c r="N462" t="n">
-        <v>17075.989515789</v>
+        <v>17112.014810127</v>
       </c>
       <c r="O462" t="n">
-        <v>2441866.500757827</v>
+        <v>2447018.117848161</v>
       </c>
       <c r="P462" t="n">
         <v>27500</v>
@@ -21188,22 +21188,22 @@
         <v>0</v>
       </c>
       <c r="L467" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M467" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N467" t="n">
         <v>59834</v>
       </c>
       <c r="O467" t="n">
-        <v>1615518</v>
+        <v>1256514</v>
       </c>
       <c r="P467" t="n">
         <v>7900</v>
       </c>
       <c r="Q467" t="n">
-        <v>213300</v>
+        <v>165900</v>
       </c>
     </row>
     <row r="468">
@@ -22163,10 +22163,10 @@
         <v>41</v>
       </c>
       <c r="N488" t="n">
-        <v>10817</v>
+        <v>10997.283333333</v>
       </c>
       <c r="O488" t="n">
-        <v>443497</v>
+        <v>450888.616666653</v>
       </c>
       <c r="P488" t="n">
         <v>17900</v>
@@ -22209,10 +22209,10 @@
         <v>41</v>
       </c>
       <c r="N489" t="n">
-        <v>12489</v>
+        <v>12769.651685393</v>
       </c>
       <c r="O489" t="n">
-        <v>512049</v>
+        <v>523555.719101113</v>
       </c>
       <c r="P489" t="n">
         <v>20900</v>
@@ -22347,10 +22347,10 @@
         <v>16</v>
       </c>
       <c r="N492" t="n">
-        <v>15472</v>
+        <v>15602.016806723</v>
       </c>
       <c r="O492" t="n">
-        <v>247552</v>
+        <v>249632.268907568</v>
       </c>
       <c r="P492" t="n">
         <v>25900</v>
@@ -23040,10 +23040,10 @@
         <v>80</v>
       </c>
       <c r="N507" t="n">
-        <v>3306.5942675159</v>
+        <v>3306.5942583732</v>
       </c>
       <c r="O507" t="n">
-        <v>264527.541401272</v>
+        <v>264527.540669856</v>
       </c>
       <c r="P507" t="n">
         <v>4900</v>
@@ -23178,10 +23178,10 @@
         <v>237</v>
       </c>
       <c r="N510" t="n">
-        <v>2056.0812616427</v>
+        <v>2056.081010453</v>
       </c>
       <c r="O510" t="n">
-        <v>487291.2590093199</v>
+        <v>487291.199477361</v>
       </c>
       <c r="P510" t="n">
         <v>2900</v>
@@ -23270,10 +23270,10 @@
         <v>225</v>
       </c>
       <c r="N512" t="n">
-        <v>1655.9287880016</v>
+        <v>1655.9287789047</v>
       </c>
       <c r="O512" t="n">
-        <v>372583.97730036</v>
+        <v>372583.9752535575</v>
       </c>
       <c r="P512" t="n">
         <v>2500</v>
@@ -23622,25 +23622,25 @@
         <v>172</v>
       </c>
       <c r="K520" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="L520" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M520" t="n">
-        <v>172</v>
+        <v>580</v>
       </c>
       <c r="N520" t="n">
         <v>1801</v>
       </c>
       <c r="O520" t="n">
-        <v>309772</v>
+        <v>1044580</v>
       </c>
       <c r="P520" t="n">
         <v>2900</v>
       </c>
       <c r="Q520" t="n">
-        <v>498800</v>
+        <v>1682000</v>
       </c>
     </row>
     <row r="521">
@@ -23858,25 +23858,25 @@
         <v>12</v>
       </c>
       <c r="K525" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L525" t="n">
         <v>0</v>
       </c>
       <c r="M525" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="N525" t="n">
         <v>13518</v>
       </c>
       <c r="O525" t="n">
-        <v>162216</v>
+        <v>1135512</v>
       </c>
       <c r="P525" t="n">
         <v>21900</v>
       </c>
       <c r="Q525" t="n">
-        <v>262800</v>
+        <v>1839600</v>
       </c>
     </row>
     <row r="526">
@@ -24951,22 +24951,22 @@
         <v>0</v>
       </c>
       <c r="L548" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M548" t="n">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="N548" t="n">
         <v>1828.64</v>
       </c>
       <c r="O548" t="n">
-        <v>2347973.76</v>
+        <v>2344316.48</v>
       </c>
       <c r="P548" t="n">
         <v>2000</v>
       </c>
       <c r="Q548" t="n">
-        <v>2568000</v>
+        <v>2564000</v>
       </c>
     </row>
     <row r="549">
@@ -24997,22 +24997,22 @@
         <v>0</v>
       </c>
       <c r="L549" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M549" t="n">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="N549" t="n">
-        <v>1690.8700095969</v>
+        <v>1690.8700097561</v>
       </c>
       <c r="O549" t="n">
-        <v>209667.8811900156</v>
+        <v>169087.00097561</v>
       </c>
       <c r="P549" t="n">
         <v>3000</v>
       </c>
       <c r="Q549" t="n">
-        <v>372000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="550">
@@ -25505,22 +25505,22 @@
         <v>0</v>
       </c>
       <c r="L560" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M560" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="N560" t="n">
-        <v>1283.6512980769</v>
+        <v>1283.6501630435</v>
       </c>
       <c r="O560" t="n">
-        <v>128365.12980769</v>
+        <v>97557.412391306</v>
       </c>
       <c r="P560" t="n">
         <v>1900</v>
       </c>
       <c r="Q560" t="n">
-        <v>190000</v>
+        <v>144400</v>
       </c>
     </row>
     <row r="561">
@@ -25786,10 +25786,10 @@
         <v>8</v>
       </c>
       <c r="N566" t="n">
-        <v>517.29656001551</v>
+        <v>517.29673853391</v>
       </c>
       <c r="O566" t="n">
-        <v>4138.37248012408</v>
+        <v>4138.37390827128</v>
       </c>
       <c r="P566" t="n">
         <v>900</v>
@@ -25971,10 +25971,10 @@
         <v>1047</v>
       </c>
       <c r="N570" t="n">
-        <v>703.79459507493</v>
+        <v>703.79459259958</v>
       </c>
       <c r="O570" t="n">
-        <v>736872.9410434518</v>
+        <v>736872.9384517603</v>
       </c>
       <c r="P570" t="n">
         <v>900</v>
@@ -26656,10 +26656,10 @@
         <v>3</v>
       </c>
       <c r="N584" t="n">
-        <v>16041.19</v>
+        <v>19605.898888889</v>
       </c>
       <c r="O584" t="n">
-        <v>48123.57</v>
+        <v>58817.69666666701</v>
       </c>
       <c r="P584" t="n">
         <v>40000</v>
@@ -26979,22 +26979,22 @@
         <v>0</v>
       </c>
       <c r="L591" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M591" t="n">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="N591" t="n">
         <v>1669.6</v>
       </c>
       <c r="O591" t="n">
-        <v>859844</v>
+        <v>856504.7999999999</v>
       </c>
       <c r="P591" t="n">
         <v>2900</v>
       </c>
       <c r="Q591" t="n">
-        <v>1493500</v>
+        <v>1487700</v>
       </c>
     </row>
     <row r="592">
@@ -27650,10 +27650,10 @@
         <v>4</v>
       </c>
       <c r="N605" t="n">
-        <v>13164.13</v>
+        <v>15985.015</v>
       </c>
       <c r="O605" t="n">
-        <v>52656.52</v>
+        <v>63940.06</v>
       </c>
       <c r="P605" t="n">
         <v>39900</v>
@@ -28229,22 +28229,22 @@
         <v>0</v>
       </c>
       <c r="L617" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M617" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N617" t="n">
-        <v>2992.5766666667</v>
+        <v>4208.3109375</v>
       </c>
       <c r="O617" t="n">
-        <v>38903.4966666671</v>
+        <v>0</v>
       </c>
       <c r="P617" t="n">
         <v>6000</v>
       </c>
       <c r="Q617" t="n">
-        <v>78000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="618">
@@ -28716,10 +28716,10 @@
         <v>16</v>
       </c>
       <c r="N627" t="n">
-        <v>3067.0906293706</v>
+        <v>3099.6039575972</v>
       </c>
       <c r="O627" t="n">
-        <v>49073.4500699296</v>
+        <v>49593.6633215552</v>
       </c>
       <c r="P627" t="n">
         <v>7200</v>
@@ -29377,10 +29377,10 @@
         <v>8</v>
       </c>
       <c r="N641" t="n">
-        <v>10737.5255</v>
+        <v>10737.525384615</v>
       </c>
       <c r="O641" t="n">
-        <v>85900.204</v>
+        <v>85900.20307692001</v>
       </c>
       <c r="P641" t="n">
         <v>18900</v>
@@ -29521,10 +29521,10 @@
         <v>3</v>
       </c>
       <c r="N644" t="n">
-        <v>36004.28</v>
+        <v>43719.482857143</v>
       </c>
       <c r="O644" t="n">
-        <v>108012.84</v>
+        <v>131158.448571429</v>
       </c>
       <c r="P644" t="n">
         <v>83500</v>
@@ -29616,10 +29616,10 @@
         <v>29</v>
       </c>
       <c r="N646" t="n">
-        <v>14751.820338983</v>
+        <v>15571.365925926</v>
       </c>
       <c r="O646" t="n">
-        <v>427802.789830507</v>
+        <v>451569.611851854</v>
       </c>
       <c r="P646" t="n">
         <v>37100</v>
@@ -29711,10 +29711,10 @@
         <v>28</v>
       </c>
       <c r="N648" t="n">
-        <v>15347.45</v>
+        <v>15516.103296703</v>
       </c>
       <c r="O648" t="n">
-        <v>429728.6</v>
+        <v>434450.892307684</v>
       </c>
       <c r="P648" t="n">
         <v>23900</v>
@@ -29950,10 +29950,10 @@
         <v>18</v>
       </c>
       <c r="N653" t="n">
-        <v>5216.9</v>
+        <v>5254.1635714286</v>
       </c>
       <c r="O653" t="n">
-        <v>93904.2</v>
+        <v>94574.94428571481</v>
       </c>
       <c r="P653" t="n">
         <v>20500</v>
@@ -30427,10 +30427,10 @@
         <v>7</v>
       </c>
       <c r="N663" t="n">
-        <v>24338.47</v>
+        <v>24856.309787234</v>
       </c>
       <c r="O663" t="n">
-        <v>170369.29</v>
+        <v>173994.168510638</v>
       </c>
       <c r="P663" t="n">
         <v>27900</v>
@@ -30660,22 +30660,22 @@
         <v>0</v>
       </c>
       <c r="L668" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M668" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="N668" t="n">
         <v>1080.18</v>
       </c>
       <c r="O668" t="n">
-        <v>347817.96</v>
+        <v>344577.42</v>
       </c>
       <c r="P668" t="n">
         <v>4900</v>
       </c>
       <c r="Q668" t="n">
-        <v>1577800</v>
+        <v>1563100</v>
       </c>
     </row>
     <row r="669">
@@ -31124,22 +31124,22 @@
         <v>0</v>
       </c>
       <c r="L678" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M678" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N678" t="n">
         <v>6761.25</v>
       </c>
       <c r="O678" t="n">
-        <v>1156173.75</v>
+        <v>1135890</v>
       </c>
       <c r="P678" t="n">
         <v>5200</v>
       </c>
       <c r="Q678" t="n">
-        <v>889200</v>
+        <v>873600</v>
       </c>
     </row>
     <row r="679">
@@ -31546,22 +31546,22 @@
         <v>0</v>
       </c>
       <c r="L687" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M687" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N687" t="n">
         <v>5077</v>
       </c>
       <c r="O687" t="n">
-        <v>167541</v>
+        <v>157387</v>
       </c>
       <c r="P687" t="n">
         <v>8500</v>
       </c>
       <c r="Q687" t="n">
-        <v>280500</v>
+        <v>263500</v>
       </c>
     </row>
     <row r="688">
@@ -31868,22 +31868,22 @@
         <v>0</v>
       </c>
       <c r="L694" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M694" t="n">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="N694" t="n">
-        <v>5218.9109399478</v>
+        <v>5506.4542424242</v>
       </c>
       <c r="O694" t="n">
-        <v>1988405.068120112</v>
+        <v>1987829.981515136</v>
       </c>
       <c r="P694" t="n">
         <v>6500</v>
       </c>
       <c r="Q694" t="n">
-        <v>2476500</v>
+        <v>2346500</v>
       </c>
     </row>
     <row r="695">
@@ -31914,22 +31914,22 @@
         <v>0</v>
       </c>
       <c r="L695" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M695" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N695" t="n">
         <v>5850</v>
       </c>
       <c r="O695" t="n">
-        <v>46800</v>
+        <v>23400</v>
       </c>
       <c r="P695" t="n">
         <v>7900</v>
       </c>
       <c r="Q695" t="n">
-        <v>63200</v>
+        <v>31600</v>
       </c>
     </row>
     <row r="696">
@@ -32144,22 +32144,22 @@
         <v>0</v>
       </c>
       <c r="L700" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M700" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N700" t="n">
         <v>31500</v>
       </c>
       <c r="O700" t="n">
-        <v>1701000</v>
+        <v>1669500</v>
       </c>
       <c r="P700" t="n">
         <v>39500</v>
       </c>
       <c r="Q700" t="n">
-        <v>2133000</v>
+        <v>2093500</v>
       </c>
     </row>
     <row r="701">
@@ -32972,22 +32972,22 @@
         <v>0</v>
       </c>
       <c r="L718" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M718" t="n">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="N718" t="n">
         <v>2376</v>
       </c>
       <c r="O718" t="n">
-        <v>1311552</v>
+        <v>1283040</v>
       </c>
       <c r="P718" t="n">
         <v>3000</v>
       </c>
       <c r="Q718" t="n">
-        <v>1656000</v>
+        <v>1620000</v>
       </c>
     </row>
     <row r="719">
@@ -33018,22 +33018,22 @@
         <v>0</v>
       </c>
       <c r="L719" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M719" t="n">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="N719" t="n">
         <v>1584</v>
       </c>
       <c r="O719" t="n">
-        <v>536976</v>
+        <v>517968</v>
       </c>
       <c r="P719" t="n">
         <v>2000</v>
       </c>
       <c r="Q719" t="n">
-        <v>678000</v>
+        <v>654000</v>
       </c>
     </row>
     <row r="720">
@@ -33064,22 +33064,22 @@
         <v>0</v>
       </c>
       <c r="L720" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M720" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="N720" t="n">
         <v>3872</v>
       </c>
       <c r="O720" t="n">
-        <v>619520</v>
+        <v>596288</v>
       </c>
       <c r="P720" t="n">
         <v>4900</v>
       </c>
       <c r="Q720" t="n">
-        <v>784000</v>
+        <v>754600</v>
       </c>
     </row>
     <row r="721">
@@ -33110,22 +33110,22 @@
         <v>0</v>
       </c>
       <c r="L721" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M721" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="N721" t="n">
         <v>3872</v>
       </c>
       <c r="O721" t="n">
-        <v>143264</v>
+        <v>120032</v>
       </c>
       <c r="P721" t="n">
         <v>4900</v>
       </c>
       <c r="Q721" t="n">
-        <v>181300</v>
+        <v>151900</v>
       </c>
     </row>
     <row r="722">
@@ -33156,22 +33156,22 @@
         <v>0</v>
       </c>
       <c r="L722" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M722" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="N722" t="n">
         <v>3872</v>
       </c>
       <c r="O722" t="n">
-        <v>809248</v>
+        <v>793760</v>
       </c>
       <c r="P722" t="n">
         <v>4900</v>
       </c>
       <c r="Q722" t="n">
-        <v>1024100</v>
+        <v>1004500</v>
       </c>
     </row>
     <row r="723">
@@ -33202,22 +33202,22 @@
         <v>0</v>
       </c>
       <c r="L723" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M723" t="n">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="N723" t="n">
         <v>6160</v>
       </c>
       <c r="O723" t="n">
-        <v>1010240</v>
+        <v>985600</v>
       </c>
       <c r="P723" t="n">
         <v>7900</v>
       </c>
       <c r="Q723" t="n">
-        <v>1295600</v>
+        <v>1264000</v>
       </c>
     </row>
     <row r="724">
@@ -33248,22 +33248,22 @@
         <v>0</v>
       </c>
       <c r="L724" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M724" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N724" t="n">
         <v>6160</v>
       </c>
       <c r="O724" t="n">
-        <v>1065680</v>
+        <v>1041040</v>
       </c>
       <c r="P724" t="n">
         <v>7900</v>
       </c>
       <c r="Q724" t="n">
-        <v>1366700</v>
+        <v>1335100</v>
       </c>
     </row>
     <row r="725">
@@ -33294,22 +33294,22 @@
         <v>0</v>
       </c>
       <c r="L725" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M725" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="N725" t="n">
         <v>6160</v>
       </c>
       <c r="O725" t="n">
-        <v>1096480</v>
+        <v>1071840</v>
       </c>
       <c r="P725" t="n">
         <v>7900</v>
       </c>
       <c r="Q725" t="n">
-        <v>1406200</v>
+        <v>1374600</v>
       </c>
     </row>
     <row r="726">
@@ -33340,22 +33340,22 @@
         <v>0</v>
       </c>
       <c r="L726" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M726" t="n">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="N726" t="n">
         <v>3344</v>
       </c>
       <c r="O726" t="n">
-        <v>785840</v>
+        <v>759088</v>
       </c>
       <c r="P726" t="n">
         <v>4500</v>
       </c>
       <c r="Q726" t="n">
-        <v>1057500</v>
+        <v>1021500</v>
       </c>
     </row>
     <row r="727">
@@ -33386,22 +33386,22 @@
         <v>0</v>
       </c>
       <c r="L727" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M727" t="n">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="N727" t="n">
         <v>3344</v>
       </c>
       <c r="O727" t="n">
-        <v>896192</v>
+        <v>869440</v>
       </c>
       <c r="P727" t="n">
         <v>4500</v>
       </c>
       <c r="Q727" t="n">
-        <v>1206000</v>
+        <v>1170000</v>
       </c>
     </row>
     <row r="728">
@@ -33432,22 +33432,22 @@
         <v>0</v>
       </c>
       <c r="L728" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M728" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N728" t="n">
         <v>4400</v>
       </c>
       <c r="O728" t="n">
-        <v>224400</v>
+        <v>206800</v>
       </c>
       <c r="P728" t="n">
         <v>5900</v>
       </c>
       <c r="Q728" t="n">
-        <v>300900</v>
+        <v>277300</v>
       </c>
     </row>
     <row r="729">
@@ -33527,22 +33527,22 @@
         <v>0</v>
       </c>
       <c r="L730" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M730" t="n">
-        <v>897</v>
+        <v>877</v>
       </c>
       <c r="N730" t="n">
         <v>1056</v>
       </c>
       <c r="O730" t="n">
-        <v>947232</v>
+        <v>926112</v>
       </c>
       <c r="P730" t="n">
         <v>1400</v>
       </c>
       <c r="Q730" t="n">
-        <v>1255800</v>
+        <v>1227800</v>
       </c>
     </row>
     <row r="731">
@@ -33714,22 +33714,22 @@
         <v>0</v>
       </c>
       <c r="L734" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M734" t="n">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="N734" t="n">
-        <v>9240</v>
+        <v>9401.162790697699</v>
       </c>
       <c r="O734" t="n">
-        <v>2448600</v>
+        <v>2350290.697674425</v>
       </c>
       <c r="P734" t="n">
         <v>11500</v>
       </c>
       <c r="Q734" t="n">
-        <v>3047500</v>
+        <v>2875000</v>
       </c>
     </row>
     <row r="735">
@@ -35115,10 +35115,10 @@
         <v>47</v>
       </c>
       <c r="N764" t="n">
-        <v>15452.21</v>
+        <v>16024.514074074</v>
       </c>
       <c r="O764" t="n">
-        <v>726253.87</v>
+        <v>753152.161481478</v>
       </c>
       <c r="P764" t="n">
         <v>36500</v>
@@ -35853,22 +35853,22 @@
         <v>0</v>
       </c>
       <c r="L780" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M780" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="N780" t="n">
         <v>2210</v>
       </c>
       <c r="O780" t="n">
-        <v>234260</v>
+        <v>225420</v>
       </c>
       <c r="P780" t="n">
         <v>2700</v>
       </c>
       <c r="Q780" t="n">
-        <v>286200</v>
+        <v>275400</v>
       </c>
     </row>
     <row r="781">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -865,10 +865,10 @@
         <v>9</v>
       </c>
       <c r="N11" t="n">
-        <v>27109.756097561</v>
+        <v>27000</v>
       </c>
       <c r="O11" t="n">
-        <v>243987.804878049</v>
+        <v>243000</v>
       </c>
       <c r="P11" t="n">
         <v>20000</v>
@@ -950,10 +950,10 @@
         <v>21</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3112820513</v>
+        <v>1811.3108641975</v>
       </c>
       <c r="O13" t="n">
-        <v>38037.5369230773</v>
+        <v>38037.5281481475</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -6422,22 +6422,22 @@
         <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M141" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="N141" t="n">
         <v>3562.46</v>
       </c>
       <c r="O141" t="n">
-        <v>170998.08</v>
+        <v>149623.32</v>
       </c>
       <c r="P141" t="n">
         <v>3000</v>
       </c>
       <c r="Q141" t="n">
-        <v>144000</v>
+        <v>126000</v>
       </c>
     </row>
     <row r="142">
@@ -7135,10 +7135,10 @@
         <v>126</v>
       </c>
       <c r="N157" t="n">
-        <v>2582.25476203</v>
+        <v>2586.3633253779</v>
       </c>
       <c r="O157" t="n">
-        <v>325364.10001578</v>
+        <v>325881.7789976154</v>
       </c>
       <c r="P157" t="n">
         <v>4500</v>
@@ -9273,10 +9273,10 @@
         <v>162</v>
       </c>
       <c r="N204" t="n">
-        <v>3472.2763744227</v>
+        <v>3472.276379862</v>
       </c>
       <c r="O204" t="n">
-        <v>562508.7726564774</v>
+        <v>562508.773537644</v>
       </c>
       <c r="P204" t="n">
         <v>5900</v>
@@ -10312,10 +10312,10 @@
         <v>170</v>
       </c>
       <c r="N227" t="n">
-        <v>4768.3543630573</v>
+        <v>4635.49</v>
       </c>
       <c r="O227" t="n">
-        <v>810620.241719741</v>
+        <v>788033.2999999999</v>
       </c>
       <c r="P227" t="n">
         <v>7500</v>
@@ -11903,10 +11903,10 @@
         <v>129</v>
       </c>
       <c r="N263" t="n">
-        <v>2029.8742541123</v>
+        <v>2029.8742613636</v>
       </c>
       <c r="O263" t="n">
-        <v>261853.7787804867</v>
+        <v>261853.7797159044</v>
       </c>
       <c r="P263" t="n">
         <v>3600</v>
@@ -12377,10 +12377,10 @@
         <v>53</v>
       </c>
       <c r="N274" t="n">
-        <v>30745.062773723</v>
+        <v>30611</v>
       </c>
       <c r="O274" t="n">
-        <v>1629488.327007319</v>
+        <v>1622383</v>
       </c>
       <c r="P274" t="n">
         <v>38900</v>
@@ -12515,10 +12515,10 @@
         <v>73</v>
       </c>
       <c r="N277" t="n">
-        <v>6207.9882003658</v>
+        <v>6207.9882013781</v>
       </c>
       <c r="O277" t="n">
-        <v>453183.1386267034</v>
+        <v>453183.1387006013</v>
       </c>
       <c r="P277" t="n">
         <v>9900</v>
@@ -12915,10 +12915,10 @@
         <v>70</v>
       </c>
       <c r="N286" t="n">
-        <v>4814.2633472037</v>
+        <v>4814.2633516301</v>
       </c>
       <c r="O286" t="n">
-        <v>336998.434304259</v>
+        <v>336998.434614107</v>
       </c>
       <c r="P286" t="n">
         <v>9900</v>
@@ -13272,22 +13272,22 @@
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M294" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N294" t="n">
         <v>22730.48</v>
       </c>
       <c r="O294" t="n">
-        <v>841027.76</v>
+        <v>818297.28</v>
       </c>
       <c r="P294" t="n">
         <v>36900</v>
       </c>
       <c r="Q294" t="n">
-        <v>1365300</v>
+        <v>1328400</v>
       </c>
     </row>
     <row r="295">
@@ -13503,10 +13503,10 @@
         <v>7</v>
       </c>
       <c r="N299" t="n">
-        <v>27123.764610526</v>
+        <v>27123.764587738</v>
       </c>
       <c r="O299" t="n">
-        <v>189866.352273682</v>
+        <v>189866.352114166</v>
       </c>
       <c r="P299" t="n">
         <v>44500</v>
@@ -13943,10 +13943,10 @@
         <v>31</v>
       </c>
       <c r="N309" t="n">
-        <v>27080.935211268</v>
+        <v>26854</v>
       </c>
       <c r="O309" t="n">
-        <v>839508.9915493079</v>
+        <v>832474</v>
       </c>
       <c r="P309" t="n">
         <v>43900</v>
@@ -15536,10 +15536,10 @@
         <v>20</v>
       </c>
       <c r="N344" t="n">
-        <v>9188.98</v>
+        <v>9456.2957818182</v>
       </c>
       <c r="O344" t="n">
-        <v>183779.6</v>
+        <v>189125.915636364</v>
       </c>
       <c r="P344" t="n">
         <v>12900</v>
@@ -15904,10 +15904,10 @@
         <v>9</v>
       </c>
       <c r="N352" t="n">
-        <v>23521.621025641</v>
+        <v>23521.620277778</v>
       </c>
       <c r="O352" t="n">
-        <v>211694.589230769</v>
+        <v>211694.582500002</v>
       </c>
       <c r="P352" t="n">
         <v>39000</v>
@@ -15996,10 +15996,10 @@
         <v>65</v>
       </c>
       <c r="N354" t="n">
-        <v>22935.194995686</v>
+        <v>22739</v>
       </c>
       <c r="O354" t="n">
-        <v>1490787.67471959</v>
+        <v>1478035</v>
       </c>
       <c r="P354" t="n">
         <v>36900</v>
@@ -17666,10 +17666,10 @@
         <v>14</v>
       </c>
       <c r="N390" t="n">
-        <v>12344.273972603</v>
+        <v>11857</v>
       </c>
       <c r="O390" t="n">
-        <v>172819.835616442</v>
+        <v>165998</v>
       </c>
       <c r="P390" t="n">
         <v>19900</v>
@@ -17850,10 +17850,10 @@
         <v>8</v>
       </c>
       <c r="N394" t="n">
-        <v>28661.941747573</v>
+        <v>28116</v>
       </c>
       <c r="O394" t="n">
-        <v>229295.533980584</v>
+        <v>224928</v>
       </c>
       <c r="P394" t="n">
         <v>45900</v>
@@ -18037,10 +18037,10 @@
         <v>51</v>
       </c>
       <c r="N398" t="n">
-        <v>10411</v>
+        <v>10642.355555556</v>
       </c>
       <c r="O398" t="n">
-        <v>530961</v>
+        <v>542760.133333356</v>
       </c>
       <c r="P398" t="n">
         <v>16900</v>
@@ -19277,10 +19277,10 @@
         <v>17</v>
       </c>
       <c r="N425" t="n">
-        <v>21286.162162162</v>
+        <v>20726</v>
       </c>
       <c r="O425" t="n">
-        <v>361864.756756754</v>
+        <v>352342</v>
       </c>
       <c r="P425" t="n">
         <v>33900</v>
@@ -19364,10 +19364,10 @@
         <v>35</v>
       </c>
       <c r="N427" t="n">
-        <v>21767.55</v>
+        <v>20731</v>
       </c>
       <c r="O427" t="n">
-        <v>761864.25</v>
+        <v>725585</v>
       </c>
       <c r="P427" t="n">
         <v>33900</v>
@@ -19456,10 +19456,10 @@
         <v>23</v>
       </c>
       <c r="N429" t="n">
-        <v>33000</v>
+        <v>35444.444444444</v>
       </c>
       <c r="O429" t="n">
-        <v>759000</v>
+        <v>815222.222222212</v>
       </c>
       <c r="P429" t="n">
         <v>52900</v>
@@ -20284,10 +20284,10 @@
         <v>19</v>
       </c>
       <c r="N447" t="n">
-        <v>13585.998452012</v>
+        <v>13565</v>
       </c>
       <c r="O447" t="n">
-        <v>258133.970588228</v>
+        <v>257735</v>
       </c>
       <c r="P447" t="n">
         <v>22500</v>
@@ -20560,10 +20560,10 @@
         <v>46</v>
       </c>
       <c r="N453" t="n">
-        <v>19059.165545087</v>
+        <v>19008</v>
       </c>
       <c r="O453" t="n">
-        <v>876721.615074002</v>
+        <v>874368</v>
       </c>
       <c r="P453" t="n">
         <v>30900</v>
@@ -20652,10 +20652,10 @@
         <v>51</v>
       </c>
       <c r="N455" t="n">
-        <v>18038.854166667</v>
+        <v>17992</v>
       </c>
       <c r="O455" t="n">
-        <v>919981.562500017</v>
+        <v>917592</v>
       </c>
       <c r="P455" t="n">
         <v>28900</v>
@@ -20836,10 +20836,10 @@
         <v>143</v>
       </c>
       <c r="N459" t="n">
-        <v>17112.014810127</v>
+        <v>17075.989514768</v>
       </c>
       <c r="O459" t="n">
-        <v>2447018.117848161</v>
+        <v>2441866.500611824</v>
       </c>
       <c r="P459" t="n">
         <v>27500</v>
@@ -22076,10 +22076,10 @@
         <v>41</v>
       </c>
       <c r="N486" t="n">
-        <v>12769.651685393</v>
+        <v>12489</v>
       </c>
       <c r="O486" t="n">
-        <v>523555.719101113</v>
+        <v>512049</v>
       </c>
       <c r="P486" t="n">
         <v>20900</v>
@@ -22214,10 +22214,10 @@
         <v>16</v>
       </c>
       <c r="N489" t="n">
-        <v>15602.016806723</v>
+        <v>15472</v>
       </c>
       <c r="O489" t="n">
-        <v>249632.268907568</v>
+        <v>247552</v>
       </c>
       <c r="P489" t="n">
         <v>25900</v>
@@ -22631,10 +22631,10 @@
         <v>238</v>
       </c>
       <c r="N498" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386990066</v>
       </c>
       <c r="O498" t="n">
-        <v>360817.209970371</v>
+        <v>360817.2103635708</v>
       </c>
       <c r="P498" t="n">
         <v>2300</v>
@@ -22861,10 +22861,10 @@
         <v>77</v>
       </c>
       <c r="N503" t="n">
-        <v>1803.0176111361</v>
+        <v>1803.0176523702</v>
       </c>
       <c r="O503" t="n">
-        <v>138832.3560574797</v>
+        <v>138832.3592325054</v>
       </c>
       <c r="P503" t="n">
         <v>2500</v>
@@ -22953,10 +22953,10 @@
         <v>487</v>
       </c>
       <c r="N505" t="n">
-        <v>2122.1634163581</v>
+        <v>2122.1634141414</v>
       </c>
       <c r="O505" t="n">
-        <v>1033493.583766395</v>
+        <v>1033493.582686862</v>
       </c>
       <c r="P505" t="n">
         <v>2900</v>
@@ -23091,10 +23091,10 @@
         <v>292</v>
       </c>
       <c r="N508" t="n">
-        <v>3224.5700336323</v>
+        <v>3224.5700392597</v>
       </c>
       <c r="O508" t="n">
-        <v>941574.4498206315</v>
+        <v>941574.4514638324</v>
       </c>
       <c r="P508" t="n">
         <v>4500</v>
@@ -23137,10 +23137,10 @@
         <v>225</v>
       </c>
       <c r="N509" t="n">
-        <v>1655.9287789047</v>
+        <v>1655.9286125978</v>
       </c>
       <c r="O509" t="n">
-        <v>372583.9752535575</v>
+        <v>372583.937834505</v>
       </c>
       <c r="P509" t="n">
         <v>2500</v>
@@ -23365,10 +23365,10 @@
         <v>772</v>
       </c>
       <c r="N514" t="n">
-        <v>1259.2752009274</v>
+        <v>1259.2751769231</v>
       </c>
       <c r="O514" t="n">
-        <v>972160.4551159528</v>
+        <v>972160.4365846332</v>
       </c>
       <c r="P514" t="n">
         <v>1900</v>
@@ -24121,10 +24121,10 @@
         <v>123</v>
       </c>
       <c r="N530" t="n">
-        <v>8945.379999999999</v>
+        <v>8949.4124778362</v>
       </c>
       <c r="O530" t="n">
-        <v>1100281.74</v>
+        <v>1100777.734773853</v>
       </c>
       <c r="P530" t="n">
         <v>14900</v>
@@ -25653,10 +25653,10 @@
         <v>8</v>
       </c>
       <c r="N563" t="n">
-        <v>517.29691759113</v>
+        <v>517.29686746988</v>
       </c>
       <c r="O563" t="n">
-        <v>4138.37534072904</v>
+        <v>4138.37493975904</v>
       </c>
       <c r="P563" t="n">
         <v>900</v>
@@ -25838,10 +25838,10 @@
         <v>1047</v>
       </c>
       <c r="N567" t="n">
-        <v>703.79458866348</v>
+        <v>703.7945904135599</v>
       </c>
       <c r="O567" t="n">
-        <v>736872.9343306635</v>
+        <v>736872.9361629973</v>
       </c>
       <c r="P567" t="n">
         <v>900</v>
@@ -26523,10 +26523,10 @@
         <v>3</v>
       </c>
       <c r="N581" t="n">
-        <v>19605.898888889</v>
+        <v>16041.19</v>
       </c>
       <c r="O581" t="n">
-        <v>58817.69666666701</v>
+        <v>48123.57</v>
       </c>
       <c r="P581" t="n">
         <v>40000</v>
@@ -27517,10 +27517,10 @@
         <v>4</v>
       </c>
       <c r="N602" t="n">
-        <v>15985.015</v>
+        <v>13164.13</v>
       </c>
       <c r="O602" t="n">
-        <v>63940.06</v>
+        <v>52656.52</v>
       </c>
       <c r="P602" t="n">
         <v>39900</v>
@@ -27762,10 +27762,10 @@
         <v>13</v>
       </c>
       <c r="N607" t="n">
-        <v>9746.8802061856</v>
+        <v>9746.8802105263</v>
       </c>
       <c r="O607" t="n">
-        <v>126709.4426804128</v>
+        <v>126709.4427368419</v>
       </c>
       <c r="P607" t="n">
         <v>18500</v>
@@ -29195,10 +29195,10 @@
         <v>8</v>
       </c>
       <c r="N637" t="n">
-        <v>10737.525384615</v>
+        <v>19429.807619048</v>
       </c>
       <c r="O637" t="n">
-        <v>85900.20307692001</v>
+        <v>155438.460952384</v>
       </c>
       <c r="P637" t="n">
         <v>18900</v>
@@ -29290,10 +29290,10 @@
         <v>3</v>
       </c>
       <c r="N639" t="n">
-        <v>43719.482857143</v>
+        <v>36004.28</v>
       </c>
       <c r="O639" t="n">
-        <v>131158.448571429</v>
+        <v>108012.84</v>
       </c>
       <c r="P639" t="n">
         <v>83500</v>
@@ -29719,10 +29719,10 @@
         <v>18</v>
       </c>
       <c r="N648" t="n">
-        <v>5254.1635714286</v>
+        <v>5216.9</v>
       </c>
       <c r="O648" t="n">
-        <v>94574.94428571481</v>
+        <v>93904.2</v>
       </c>
       <c r="P648" t="n">
         <v>20500</v>
@@ -31545,22 +31545,22 @@
         <v>0</v>
       </c>
       <c r="L687" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M687" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N687" t="n">
         <v>19800</v>
       </c>
       <c r="O687" t="n">
-        <v>79200</v>
+        <v>39600</v>
       </c>
       <c r="P687" t="n">
         <v>24900</v>
       </c>
       <c r="Q687" t="n">
-        <v>99600</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="688">
@@ -31591,22 +31591,22 @@
         <v>0</v>
       </c>
       <c r="L688" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M688" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N688" t="n">
         <v>20700</v>
       </c>
       <c r="O688" t="n">
-        <v>41400</v>
+        <v>20700</v>
       </c>
       <c r="P688" t="n">
         <v>25900</v>
       </c>
       <c r="Q688" t="n">
-        <v>51800</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="689">
@@ -32097,22 +32097,22 @@
         <v>0</v>
       </c>
       <c r="L699" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M699" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N699" t="n">
-        <v>29700</v>
+        <v>0</v>
       </c>
       <c r="O699" t="n">
-        <v>29700</v>
+        <v>0</v>
       </c>
       <c r="P699" t="n">
         <v>39900</v>
       </c>
       <c r="Q699" t="n">
-        <v>39900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="700">
@@ -34884,10 +34884,10 @@
         <v>47</v>
       </c>
       <c r="N759" t="n">
-        <v>16024.514074074</v>
+        <v>15452.21</v>
       </c>
       <c r="O759" t="n">
-        <v>753152.161481478</v>
+        <v>726253.87</v>
       </c>
       <c r="P759" t="n">
         <v>36500</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -682,25 +682,25 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N7" t="n">
         <v>74676.599</v>
       </c>
       <c r="O7" t="n">
-        <v>373382.995</v>
+        <v>672089.3910000001</v>
       </c>
       <c r="P7" t="n">
         <v>144900</v>
       </c>
       <c r="Q7" t="n">
-        <v>724500</v>
+        <v>1304100</v>
       </c>
     </row>
     <row r="8">
@@ -1290,22 +1290,22 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N22" t="n">
-        <v>15238.01</v>
+        <v>15304.843377193</v>
       </c>
       <c r="O22" t="n">
-        <v>167618.11</v>
+        <v>153048.43377193</v>
       </c>
       <c r="P22" t="n">
         <v>40400</v>
       </c>
       <c r="Q22" t="n">
-        <v>444400</v>
+        <v>404000</v>
       </c>
     </row>
     <row r="23">
@@ -1967,22 +1967,22 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N39" t="n">
-        <v>21333.69</v>
+        <v>21425.250901288</v>
       </c>
       <c r="O39" t="n">
-        <v>256004.28</v>
+        <v>235677.759914168</v>
       </c>
       <c r="P39" t="n">
         <v>30000</v>
       </c>
       <c r="Q39" t="n">
-        <v>360000</v>
+        <v>330000</v>
       </c>
     </row>
     <row r="40">
@@ -3808,25 +3808,25 @@
         <v>2</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N81" t="n">
         <v>141416.88465116</v>
       </c>
       <c r="O81" t="n">
-        <v>282833.76930232</v>
+        <v>1697002.61581392</v>
       </c>
       <c r="P81" t="n">
         <v>251900</v>
       </c>
       <c r="Q81" t="n">
-        <v>503800</v>
+        <v>3022800</v>
       </c>
     </row>
     <row r="82">
@@ -3906,10 +3906,10 @@
         <v>6</v>
       </c>
       <c r="N83" t="n">
-        <v>27000</v>
+        <v>28500</v>
       </c>
       <c r="O83" t="n">
-        <v>162000</v>
+        <v>171000</v>
       </c>
       <c r="P83" t="n">
         <v>20000</v>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3981,19 +3981,19 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N85" t="n">
         <v>1141.57</v>
       </c>
       <c r="O85" t="n">
-        <v>63927.92</v>
+        <v>62786.35</v>
       </c>
       <c r="P85" t="n">
         <v>3900</v>
       </c>
       <c r="Q85" t="n">
-        <v>218400</v>
+        <v>214500</v>
       </c>
     </row>
     <row r="86">
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -6418,19 +6418,19 @@
         <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N141" t="n">
         <v>3775.99</v>
       </c>
       <c r="O141" t="n">
-        <v>147263.61</v>
+        <v>143487.62</v>
       </c>
       <c r="P141" t="n">
         <v>7300</v>
       </c>
       <c r="Q141" t="n">
-        <v>284700</v>
+        <v>277400</v>
       </c>
     </row>
     <row r="142">
@@ -6771,22 +6771,22 @@
         <v>0</v>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M149" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="N149" t="n">
-        <v>13593.35</v>
+        <v>13694.165945612</v>
       </c>
       <c r="O149" t="n">
-        <v>516547.3</v>
+        <v>438213.310259584</v>
       </c>
       <c r="P149" t="n">
         <v>25500</v>
       </c>
       <c r="Q149" t="n">
-        <v>969000</v>
+        <v>816000</v>
       </c>
     </row>
     <row r="150">
@@ -7041,10 +7041,10 @@
         <v>126</v>
       </c>
       <c r="N155" t="n">
-        <v>2582.2547091633</v>
+        <v>2582.2546851654</v>
       </c>
       <c r="O155" t="n">
-        <v>325364.0933545758</v>
+        <v>325364.0903308404</v>
       </c>
       <c r="P155" t="n">
         <v>4500</v>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
@@ -7360,19 +7360,19 @@
         <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="N162" t="n">
         <v>156.25</v>
       </c>
       <c r="O162" t="n">
-        <v>108593.75</v>
+        <v>107031.25</v>
       </c>
       <c r="P162" t="n">
         <v>250</v>
       </c>
       <c r="Q162" t="n">
-        <v>173750</v>
+        <v>171250</v>
       </c>
     </row>
     <row r="163">
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
@@ -7815,19 +7815,19 @@
         <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="N172" t="n">
-        <v>4890.9300565371</v>
+        <v>4890.9300570207</v>
       </c>
       <c r="O172" t="n">
-        <v>371710.6842968196</v>
+        <v>313019.5236493248</v>
       </c>
       <c r="P172" t="n">
         <v>8900</v>
       </c>
       <c r="Q172" t="n">
-        <v>676400</v>
+        <v>569600</v>
       </c>
     </row>
     <row r="173">
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
@@ -8176,19 +8176,19 @@
         <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="N180" t="n">
         <v>5667.94</v>
       </c>
       <c r="O180" t="n">
-        <v>232385.54</v>
+        <v>164370.26</v>
       </c>
       <c r="P180" t="n">
         <v>9500</v>
       </c>
       <c r="Q180" t="n">
-        <v>389500</v>
+        <v>275500</v>
       </c>
     </row>
     <row r="181">
@@ -8675,22 +8675,22 @@
         <v>0</v>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N191" t="n">
-        <v>14822.378814083</v>
+        <v>14831.53974042</v>
       </c>
       <c r="O191" t="n">
-        <v>755941.319518233</v>
+        <v>741576.987021</v>
       </c>
       <c r="P191" t="n">
         <v>24900</v>
       </c>
       <c r="Q191" t="n">
-        <v>1269900</v>
+        <v>1245000</v>
       </c>
     </row>
     <row r="192">
@@ -8990,7 +8990,7 @@
         </is>
       </c>
       <c r="J198" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K198" t="n">
         <v>0</v>
@@ -8999,19 +8999,19 @@
         <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N198" t="n">
-        <v>12422.46300928</v>
+        <v>12422.463013274</v>
       </c>
       <c r="O198" t="n">
-        <v>633545.61347328</v>
+        <v>596278.224637152</v>
       </c>
       <c r="P198" t="n">
         <v>19900</v>
       </c>
       <c r="Q198" t="n">
-        <v>1014900</v>
+        <v>955200</v>
       </c>
     </row>
     <row r="199">
@@ -9179,10 +9179,10 @@
         <v>150</v>
       </c>
       <c r="N202" t="n">
-        <v>3472.276393501</v>
+        <v>3472.2764071985</v>
       </c>
       <c r="O202" t="n">
-        <v>520841.45902515</v>
+        <v>520841.4610797749</v>
       </c>
       <c r="P202" t="n">
         <v>5900</v>
@@ -9403,10 +9403,10 @@
         <v>52</v>
       </c>
       <c r="N207" t="n">
-        <v>4371.1729731899</v>
+        <v>4371.1729736673</v>
       </c>
       <c r="O207" t="n">
-        <v>227300.9946058748</v>
+        <v>227300.9946306996</v>
       </c>
       <c r="P207" t="n">
         <v>8900</v>
@@ -10218,10 +10218,10 @@
         <v>167</v>
       </c>
       <c r="N225" t="n">
-        <v>4635.49</v>
+        <v>4680.6408766234</v>
       </c>
       <c r="O225" t="n">
-        <v>774126.83</v>
+        <v>781667.0263961077</v>
       </c>
       <c r="P225" t="n">
         <v>7500</v>
@@ -11207,10 +11207,10 @@
         <v>25</v>
       </c>
       <c r="N247" t="n">
-        <v>18071.26</v>
+        <v>18238.586481481</v>
       </c>
       <c r="O247" t="n">
-        <v>451781.4999999999</v>
+        <v>455964.662037025</v>
       </c>
       <c r="P247" t="n">
         <v>23900</v>
@@ -12589,7 +12589,7 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -12598,19 +12598,19 @@
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N279" t="n">
         <v>16275</v>
       </c>
       <c r="O279" t="n">
-        <v>292950</v>
+        <v>276675</v>
       </c>
       <c r="P279" t="n">
         <v>27600</v>
       </c>
       <c r="Q279" t="n">
-        <v>496800</v>
+        <v>469200</v>
       </c>
     </row>
     <row r="280">
@@ -12775,10 +12775,10 @@
         <v>68</v>
       </c>
       <c r="N283" t="n">
-        <v>4814.2633494176</v>
+        <v>4814.2633472037</v>
       </c>
       <c r="O283" t="n">
-        <v>327369.9077603968</v>
+        <v>327369.9076098516</v>
       </c>
       <c r="P283" t="n">
         <v>7900</v>
@@ -12908,10 +12908,10 @@
         <v>32</v>
       </c>
       <c r="N286" t="n">
-        <v>13513.644019608</v>
+        <v>13513.644059406</v>
       </c>
       <c r="O286" t="n">
-        <v>432436.608627456</v>
+        <v>432436.609900992</v>
       </c>
       <c r="P286" t="n">
         <v>21900</v>
@@ -13126,7 +13126,7 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
@@ -13135,19 +13135,19 @@
         <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N291" t="n">
         <v>22730.48</v>
       </c>
       <c r="O291" t="n">
-        <v>818297.28</v>
+        <v>772836.3199999999</v>
       </c>
       <c r="P291" t="n">
         <v>36900</v>
       </c>
       <c r="Q291" t="n">
-        <v>1328400</v>
+        <v>1254600</v>
       </c>
     </row>
     <row r="292">
@@ -13363,10 +13363,10 @@
         <v>7</v>
       </c>
       <c r="N296" t="n">
-        <v>27123.764587738</v>
+        <v>27123.764576271</v>
       </c>
       <c r="O296" t="n">
-        <v>189866.352114166</v>
+        <v>189866.352033897</v>
       </c>
       <c r="P296" t="n">
         <v>44500</v>
@@ -14244,10 +14244,10 @@
         <v>33</v>
       </c>
       <c r="N316" t="n">
-        <v>12981.59</v>
+        <v>13033.935120968</v>
       </c>
       <c r="O316" t="n">
-        <v>428392.47</v>
+        <v>430119.858991944</v>
       </c>
       <c r="P316" t="n">
         <v>21900</v>
@@ -15355,10 +15355,10 @@
         <v>20</v>
       </c>
       <c r="N340" t="n">
-        <v>9188.98</v>
+        <v>9254.3819928826</v>
       </c>
       <c r="O340" t="n">
-        <v>183779.6</v>
+        <v>185087.639857652</v>
       </c>
       <c r="P340" t="n">
         <v>12900</v>
@@ -15435,7 +15435,7 @@
         </is>
       </c>
       <c r="J342" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K342" t="n">
         <v>0</v>
@@ -15444,19 +15444,19 @@
         <v>0</v>
       </c>
       <c r="M342" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N342" t="n">
         <v>18536</v>
       </c>
       <c r="O342" t="n">
-        <v>704368</v>
+        <v>685832</v>
       </c>
       <c r="P342" t="n">
         <v>30900</v>
       </c>
       <c r="Q342" t="n">
-        <v>1174200</v>
+        <v>1143300</v>
       </c>
     </row>
     <row r="343">
@@ -15947,22 +15947,22 @@
         <v>0</v>
       </c>
       <c r="L353" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M353" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N353" t="n">
-        <v>25534</v>
+        <v>25577.697661152</v>
       </c>
       <c r="O353" t="n">
-        <v>638350</v>
+        <v>562709.348545344</v>
       </c>
       <c r="P353" t="n">
         <v>40900</v>
       </c>
       <c r="Q353" t="n">
-        <v>1022500</v>
+        <v>899800</v>
       </c>
     </row>
     <row r="354">
@@ -16588,7 +16588,7 @@
         </is>
       </c>
       <c r="J367" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K367" t="n">
         <v>0</v>
@@ -16597,19 +16597,19 @@
         <v>0</v>
       </c>
       <c r="M367" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N367" t="n">
-        <v>3259.2102666667</v>
+        <v>3259.2102702703</v>
       </c>
       <c r="O367" t="n">
-        <v>104294.7285333344</v>
+        <v>101035.5183783793</v>
       </c>
       <c r="P367" t="n">
         <v>5300</v>
       </c>
       <c r="Q367" t="n">
-        <v>169600</v>
+        <v>164300</v>
       </c>
     </row>
     <row r="368">
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="J377" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K377" t="n">
         <v>0</v>
@@ -17062,19 +17062,19 @@
         <v>0</v>
       </c>
       <c r="M377" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N377" t="n">
         <v>1550</v>
       </c>
       <c r="O377" t="n">
-        <v>52700</v>
+        <v>51150</v>
       </c>
       <c r="P377" t="n">
         <v>2500</v>
       </c>
       <c r="Q377" t="n">
-        <v>85000</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="378">
@@ -17485,10 +17485,10 @@
         <v>8</v>
       </c>
       <c r="N386" t="n">
-        <v>11857</v>
+        <v>12039.415384615</v>
       </c>
       <c r="O386" t="n">
-        <v>94856</v>
+        <v>96315.32307692</v>
       </c>
       <c r="P386" t="n">
         <v>19900</v>
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="J389" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K389" t="n">
         <v>0</v>
@@ -17620,19 +17620,19 @@
         <v>0</v>
       </c>
       <c r="M389" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N389" t="n">
         <v>20049</v>
       </c>
       <c r="O389" t="n">
-        <v>380931</v>
+        <v>360882</v>
       </c>
       <c r="P389" t="n">
         <v>32900</v>
       </c>
       <c r="Q389" t="n">
-        <v>625100</v>
+        <v>592200</v>
       </c>
     </row>
     <row r="390">
@@ -17856,10 +17856,10 @@
         <v>51</v>
       </c>
       <c r="N394" t="n">
-        <v>10411</v>
+        <v>10448.858181818</v>
       </c>
       <c r="O394" t="n">
-        <v>530961</v>
+        <v>532891.7672727179</v>
       </c>
       <c r="P394" t="n">
         <v>16900</v>
@@ -18503,10 +18503,10 @@
         <v>29</v>
       </c>
       <c r="N408" t="n">
-        <v>9003</v>
+        <v>9018.1565656566</v>
       </c>
       <c r="O408" t="n">
-        <v>261087</v>
+        <v>261526.5404040414</v>
       </c>
       <c r="P408" t="n">
         <v>14900</v>
@@ -19539,7 +19539,7 @@
         </is>
       </c>
       <c r="J431" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K431" t="n">
         <v>0</v>
@@ -19548,19 +19548,19 @@
         <v>0</v>
       </c>
       <c r="M431" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N431" t="n">
         <v>9839</v>
       </c>
       <c r="O431" t="n">
-        <v>78712</v>
+        <v>68873</v>
       </c>
       <c r="P431" t="n">
         <v>16900</v>
       </c>
       <c r="Q431" t="n">
-        <v>135200</v>
+        <v>118300</v>
       </c>
     </row>
     <row r="432">
@@ -20471,10 +20471,10 @@
         <v>51</v>
       </c>
       <c r="N451" t="n">
-        <v>17992</v>
+        <v>18015.518954248</v>
       </c>
       <c r="O451" t="n">
-        <v>917592</v>
+        <v>918791.466666648</v>
       </c>
       <c r="P451" t="n">
         <v>28900</v>
@@ -20914,7 +20914,7 @@
         </is>
       </c>
       <c r="J461" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K461" t="n">
         <v>0</v>
@@ -20923,19 +20923,19 @@
         <v>0</v>
       </c>
       <c r="M461" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N461" t="n">
         <v>21346</v>
       </c>
       <c r="O461" t="n">
-        <v>426920</v>
+        <v>405574</v>
       </c>
       <c r="P461" t="n">
         <v>34900</v>
       </c>
       <c r="Q461" t="n">
-        <v>698000</v>
+        <v>663100</v>
       </c>
     </row>
     <row r="462">
@@ -21619,10 +21619,10 @@
         <v>33</v>
       </c>
       <c r="N476" t="n">
-        <v>8700</v>
+        <v>8711.0687022901</v>
       </c>
       <c r="O476" t="n">
-        <v>287100</v>
+        <v>287465.2671755733</v>
       </c>
       <c r="P476" t="n">
         <v>14900</v>
@@ -22033,10 +22033,10 @@
         <v>13</v>
       </c>
       <c r="N485" t="n">
-        <v>15472</v>
+        <v>15516.07977208</v>
       </c>
       <c r="O485" t="n">
-        <v>201136</v>
+        <v>201709.03703704</v>
       </c>
       <c r="P485" t="n">
         <v>25900</v>
@@ -22438,7 +22438,7 @@
         </is>
       </c>
       <c r="J494" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K494" t="n">
         <v>0</v>
@@ -22447,19 +22447,19 @@
         <v>0</v>
       </c>
       <c r="M494" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="N494" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386972166</v>
       </c>
       <c r="O494" t="n">
-        <v>342624.745602117</v>
+        <v>341108.706873735</v>
       </c>
       <c r="P494" t="n">
         <v>2300</v>
       </c>
       <c r="Q494" t="n">
-        <v>519800</v>
+        <v>517500</v>
       </c>
     </row>
     <row r="495">
@@ -22680,10 +22680,10 @@
         <v>72</v>
       </c>
       <c r="N499" t="n">
-        <v>1803.0176696833</v>
+        <v>1803.0176731553</v>
       </c>
       <c r="O499" t="n">
-        <v>129817.2722171976</v>
+        <v>129817.2724671816</v>
       </c>
       <c r="P499" t="n">
         <v>2500</v>
@@ -22714,7 +22714,7 @@
         </is>
       </c>
       <c r="J500" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K500" t="n">
         <v>0</v>
@@ -22723,19 +22723,19 @@
         <v>0</v>
       </c>
       <c r="M500" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N500" t="n">
-        <v>3306.5942675159</v>
+        <v>3306.5942492013</v>
       </c>
       <c r="O500" t="n">
-        <v>267834.1356687879</v>
+        <v>264527.539936104</v>
       </c>
       <c r="P500" t="n">
         <v>4900</v>
       </c>
       <c r="Q500" t="n">
-        <v>396900</v>
+        <v>392000</v>
       </c>
     </row>
     <row r="501">
@@ -23082,7 +23082,7 @@
         </is>
       </c>
       <c r="J508" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K508" t="n">
         <v>0</v>
@@ -23091,19 +23091,19 @@
         <v>0</v>
       </c>
       <c r="M508" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N508" t="n">
         <v>2454</v>
       </c>
       <c r="O508" t="n">
-        <v>461352</v>
+        <v>458898</v>
       </c>
       <c r="P508" t="n">
         <v>4200</v>
       </c>
       <c r="Q508" t="n">
-        <v>789600</v>
+        <v>785400</v>
       </c>
     </row>
     <row r="509">
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="J510" t="n">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="K510" t="n">
         <v>0</v>
@@ -23181,19 +23181,19 @@
         <v>0</v>
       </c>
       <c r="M510" t="n">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="N510" t="n">
-        <v>1259.2751809084</v>
+        <v>1259.2751822382</v>
       </c>
       <c r="O510" t="n">
-        <v>972160.4396612848</v>
+        <v>970901.1655056522</v>
       </c>
       <c r="P510" t="n">
         <v>1900</v>
       </c>
       <c r="Q510" t="n">
-        <v>1466800</v>
+        <v>1464900</v>
       </c>
     </row>
     <row r="511">
@@ -23553,10 +23553,10 @@
         <v>84</v>
       </c>
       <c r="N518" t="n">
-        <v>13518</v>
+        <v>13521.774923206</v>
       </c>
       <c r="O518" t="n">
-        <v>1135512</v>
+        <v>1135829.093549304</v>
       </c>
       <c r="P518" t="n">
         <v>21900</v>
@@ -23842,10 +23842,10 @@
         <v>37</v>
       </c>
       <c r="N524" t="n">
-        <v>15423.36</v>
+        <v>15547.741935484</v>
       </c>
       <c r="O524" t="n">
-        <v>570664.3200000001</v>
+        <v>575266.451612908</v>
       </c>
       <c r="P524" t="n">
         <v>24900</v>
@@ -25645,7 +25645,7 @@
         </is>
       </c>
       <c r="J563" t="n">
-        <v>999</v>
+        <v>975</v>
       </c>
       <c r="K563" t="n">
         <v>0</v>
@@ -25654,19 +25654,19 @@
         <v>0</v>
       </c>
       <c r="M563" t="n">
-        <v>999</v>
+        <v>975</v>
       </c>
       <c r="N563" t="n">
-        <v>703.79458486774</v>
+        <v>703.7945831140599</v>
       </c>
       <c r="O563" t="n">
-        <v>703090.7902828723</v>
+        <v>686199.7185362085</v>
       </c>
       <c r="P563" t="n">
         <v>900</v>
       </c>
       <c r="Q563" t="n">
-        <v>899100</v>
+        <v>877500</v>
       </c>
     </row>
     <row r="564">
@@ -26293,10 +26293,10 @@
         <v>7</v>
       </c>
       <c r="N576" t="n">
-        <v>9694.41</v>
+        <v>12723.913125</v>
       </c>
       <c r="O576" t="n">
-        <v>67860.87</v>
+        <v>89067.391875</v>
       </c>
       <c r="P576" t="n">
         <v>32500</v>
@@ -27630,10 +27630,10 @@
         <v>4</v>
       </c>
       <c r="N604" t="n">
-        <v>7653.955</v>
+        <v>8747.3771428571</v>
       </c>
       <c r="O604" t="n">
-        <v>30615.82</v>
+        <v>34989.5085714284</v>
       </c>
       <c r="P604" t="n">
         <v>11900</v>
@@ -29014,10 +29014,10 @@
         <v>8</v>
       </c>
       <c r="N633" t="n">
-        <v>10737.525135135</v>
+        <v>10737.525</v>
       </c>
       <c r="O633" t="n">
-        <v>85900.20108108</v>
+        <v>85900.2</v>
       </c>
       <c r="P633" t="n">
         <v>18900</v>
@@ -29480,7 +29480,7 @@
         </is>
       </c>
       <c r="J643" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K643" t="n">
         <v>0</v>
@@ -29489,19 +29489,19 @@
         <v>0</v>
       </c>
       <c r="M643" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N643" t="n">
         <v>13177.76</v>
       </c>
       <c r="O643" t="n">
-        <v>316266.24</v>
+        <v>289910.72</v>
       </c>
       <c r="P643" t="n">
         <v>44500</v>
       </c>
       <c r="Q643" t="n">
-        <v>1068000</v>
+        <v>979000</v>
       </c>
     </row>
     <row r="644">
@@ -33201,7 +33201,7 @@
         </is>
       </c>
       <c r="J723" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K723" t="n">
         <v>0</v>
@@ -33210,19 +33210,19 @@
         <v>0</v>
       </c>
       <c r="M723" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N723" t="n">
         <v>7216</v>
       </c>
       <c r="O723" t="n">
-        <v>28864</v>
+        <v>21648</v>
       </c>
       <c r="P723" t="n">
         <v>9000</v>
       </c>
       <c r="Q723" t="n">
-        <v>36000</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="724">
@@ -33259,10 +33259,10 @@
         <v>212</v>
       </c>
       <c r="N724" t="n">
-        <v>5280</v>
+        <v>5285.1815505397</v>
       </c>
       <c r="O724" t="n">
-        <v>1119360</v>
+        <v>1120458.488714416</v>
       </c>
       <c r="P724" t="n">
         <v>6900</v>
